--- a/data/Historico_Produccion_CREMIGURT.xlsx
+++ b/data/Historico_Produccion_CREMIGURT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B9C5599-E710-4D06-B17C-2CA9F5D834FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B24BC56-D73A-43F0-B0D6-103B1879CD93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -603,7 +603,7 @@
       <sheetData sheetId="2">
         <row r="12">
           <cell r="P12">
-            <v>233564</v>
+            <v>272908</v>
           </cell>
         </row>
       </sheetData>
@@ -613,14 +613,14 @@
             <v>500217</v>
           </cell>
           <cell r="W9">
-            <v>192392</v>
+            <v>213810</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="4">
         <row r="9">
           <cell r="L9">
-            <v>192392</v>
+            <v>213810</v>
           </cell>
         </row>
       </sheetData>
@@ -631,14 +631,14 @@
             <v>44970</v>
           </cell>
           <cell r="L7">
-            <v>17946</v>
+            <v>18249</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="7">
         <row r="10">
           <cell r="K10">
-            <v>19921</v>
+            <v>24922</v>
           </cell>
         </row>
       </sheetData>
@@ -648,7 +648,7 @@
             <v>15181</v>
           </cell>
           <cell r="J6">
-            <v>7187</v>
+            <v>11507</v>
           </cell>
         </row>
         <row r="7">
@@ -733,7 +733,7 @@
       <sheetData sheetId="10">
         <row r="11">
           <cell r="L11">
-            <v>18263</v>
+            <v>21189</v>
           </cell>
         </row>
       </sheetData>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Total Unidades Mensuales'!$P$12</f>
-        <v>233564</v>
+        <v>272908</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="H4" s="3">
         <f>(H3-G3)/G3</f>
-        <v>-0.59616225852019755</v>
+        <v>-0.52813554164267651</v>
       </c>
     </row>
   </sheetData>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Total Cremigurt Unidades'!$W$9</f>
-        <v>192392</v>
+        <v>213810</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-0.61538292381106596</v>
+        <v>-0.5725655065701486</v>
       </c>
     </row>
   </sheetData>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]150 gr'!$L$9</f>
-        <v>192392</v>
+        <v>213810</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-0.56065055651721163</v>
+        <v>-0.51174006969595942</v>
       </c>
     </row>
   </sheetData>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]700 gr'!$L$7</f>
-        <v>17946</v>
+        <v>18249</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-0.60093395597064714</v>
+        <v>-0.59419613075383593</v>
       </c>
     </row>
   </sheetData>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Linea Azul'!$K$10</f>
-        <v>19921</v>
+        <v>24922</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.66801099908340966</v>
+        <v>-0.58466794433797187</v>
       </c>
     </row>
   </sheetData>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]POWER!$J$6+[2]POWER!$J$8+[2]POWER!$J$10+[2]POWER!$J$11+[2]POWER!$J$12+[2]POWER!$J$13</f>
-        <v>32340</v>
+        <v>36660</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.59439629764338475</v>
+        <v>-0.54021546912821539</v>
       </c>
     </row>
   </sheetData>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]Cremosillo!$L$11</f>
-        <v>18263</v>
+        <v>21189</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.51199764856776397</v>
+        <v>-0.43381252672082088</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico_Produccion_CREMIGURT.xlsx
+++ b/data/Historico_Produccion_CREMIGURT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B24BC56-D73A-43F0-B0D6-103B1879CD93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6064C29F-79BC-4AE6-B7CD-D3CD1E54F8A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -603,7 +603,7 @@
       <sheetData sheetId="2">
         <row r="12">
           <cell r="P12">
-            <v>272908</v>
+            <v>295701</v>
           </cell>
         </row>
       </sheetData>
@@ -613,14 +613,14 @@
             <v>500217</v>
           </cell>
           <cell r="W9">
-            <v>213810</v>
+            <v>251220</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="4">
         <row r="9">
           <cell r="L9">
-            <v>213810</v>
+            <v>251220</v>
           </cell>
         </row>
       </sheetData>
@@ -631,14 +631,14 @@
             <v>44970</v>
           </cell>
           <cell r="L7">
-            <v>18249</v>
+            <v>21222</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="7">
         <row r="10">
           <cell r="K10">
-            <v>24922</v>
+            <v>30119</v>
           </cell>
         </row>
       </sheetData>
@@ -648,7 +648,7 @@
             <v>15181</v>
           </cell>
           <cell r="J6">
-            <v>11507</v>
+            <v>12363</v>
           </cell>
         </row>
         <row r="7">
@@ -661,7 +661,7 @@
             <v>24605</v>
           </cell>
           <cell r="J8">
-            <v>12962</v>
+            <v>16553</v>
           </cell>
         </row>
         <row r="9">
@@ -726,7 +726,7 @@
             <v>239872</v>
           </cell>
           <cell r="L18">
-            <v>81812</v>
+            <v>108766</v>
           </cell>
         </row>
       </sheetData>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Total Unidades Mensuales'!$P$12</f>
-        <v>272908</v>
+        <v>295701</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="H4" s="3">
         <f>(H3-G3)/G3</f>
-        <v>-0.52813554164267651</v>
+        <v>-0.4887258995679169</v>
       </c>
     </row>
   </sheetData>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Total Cremigurt Unidades'!$W$9</f>
-        <v>213810</v>
+        <v>251220</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-0.5725655065701486</v>
+        <v>-0.49777796436346627</v>
       </c>
     </row>
   </sheetData>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]150 gr'!$L$9</f>
-        <v>213810</v>
+        <v>251220</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-0.51174006969595942</v>
+        <v>-0.42630999630054212</v>
       </c>
     </row>
   </sheetData>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]700 gr'!$L$7</f>
-        <v>18249</v>
+        <v>21222</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-0.59419613075383593</v>
+        <v>-0.52808539026017343</v>
       </c>
     </row>
   </sheetData>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Linea Azul'!$K$10</f>
-        <v>24922</v>
+        <v>30119</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.58466794433797187</v>
+        <v>-0.49805849512540623</v>
       </c>
     </row>
   </sheetData>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]POWER!$J$6+[2]POWER!$J$8+[2]POWER!$J$10+[2]POWER!$J$11+[2]POWER!$J$12+[2]POWER!$J$13</f>
-        <v>36660</v>
+        <v>41107</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.54021546912821539</v>
+        <v>-0.48444182458956769</v>
       </c>
     </row>
   </sheetData>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]Frutas!$L$18</f>
-        <v>81812</v>
+        <v>108766</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.65893476520811101</v>
+        <v>-0.54656650213447167</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico_Produccion_CREMIGURT.xlsx
+++ b/data/Historico_Produccion_CREMIGURT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6064C29F-79BC-4AE6-B7CD-D3CD1E54F8A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE2E7AEC-86F0-4BC7-9EDD-864949DFD0D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -603,7 +603,7 @@
       <sheetData sheetId="2">
         <row r="12">
           <cell r="P12">
-            <v>295701</v>
+            <v>324175</v>
           </cell>
         </row>
       </sheetData>
@@ -613,14 +613,14 @@
             <v>500217</v>
           </cell>
           <cell r="W9">
-            <v>251220</v>
+            <v>269750</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="4">
         <row r="9">
           <cell r="L9">
-            <v>251220</v>
+            <v>269750</v>
           </cell>
         </row>
       </sheetData>
@@ -631,7 +631,7 @@
             <v>44970</v>
           </cell>
           <cell r="L7">
-            <v>21222</v>
+            <v>24242</v>
           </cell>
         </row>
       </sheetData>
@@ -653,7 +653,7 @@
         </row>
         <row r="7">
           <cell r="J7">
-            <v>880</v>
+            <v>1292</v>
           </cell>
         </row>
         <row r="8">
@@ -661,12 +661,12 @@
             <v>24605</v>
           </cell>
           <cell r="J8">
-            <v>16553</v>
+            <v>20043</v>
           </cell>
         </row>
         <row r="9">
           <cell r="J9">
-            <v>1374</v>
+            <v>1826</v>
           </cell>
         </row>
         <row r="10">
@@ -674,7 +674,7 @@
             <v>12002</v>
           </cell>
           <cell r="J10">
-            <v>2003</v>
+            <v>3915</v>
           </cell>
         </row>
         <row r="11">
@@ -733,14 +733,14 @@
       <sheetData sheetId="10">
         <row r="11">
           <cell r="L11">
-            <v>21189</v>
+            <v>25716</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="11">
         <row r="13">
           <cell r="L13">
-            <v>20584</v>
+            <v>25744</v>
           </cell>
         </row>
       </sheetData>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Total Unidades Mensuales'!$P$12</f>
-        <v>295701</v>
+        <v>324175</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="H4" s="3">
         <f>(H3-G3)/G3</f>
-        <v>-0.4887258995679169</v>
+        <v>-0.43949367263698624</v>
       </c>
     </row>
   </sheetData>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]Gelatina!$L$13</f>
-        <v>20584</v>
+        <v>25744</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.41709851895902361</v>
+        <v>-0.27097669413530429</v>
       </c>
     </row>
   </sheetData>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Total Cremigurt Unidades'!$W$9</f>
-        <v>251220</v>
+        <v>269750</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-0.49777796436346627</v>
+        <v>-0.46073404142602109</v>
       </c>
     </row>
   </sheetData>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]150 gr'!$L$9</f>
-        <v>251220</v>
+        <v>269750</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-0.42630999630054212</v>
+        <v>-0.3839945923973857</v>
       </c>
     </row>
   </sheetData>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]700 gr'!$L$7</f>
-        <v>21222</v>
+        <v>24242</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-0.52808539026017343</v>
+        <v>-0.46092950856126308</v>
       </c>
     </row>
   </sheetData>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]POWER!$J$6+[2]POWER!$J$8+[2]POWER!$J$10+[2]POWER!$J$11+[2]POWER!$J$12+[2]POWER!$J$13</f>
-        <v>41107</v>
+        <v>46509</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.48444182458956769</v>
+        <v>-0.41669070522870078</v>
       </c>
     </row>
   </sheetData>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]POWER!$J$7+[2]POWER!$J$9</f>
-        <v>2254</v>
+        <v>3118</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.63030998851894371</v>
+        <v>-0.48860095128751846</v>
       </c>
     </row>
   </sheetData>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]Cremosillo!$L$11</f>
-        <v>21189</v>
+        <v>25716</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.43381252672082088</v>
+        <v>-0.31284737067122703</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico_Produccion_CREMIGURT.xlsx
+++ b/data/Historico_Produccion_CREMIGURT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE2E7AEC-86F0-4BC7-9EDD-864949DFD0D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1165E0F-A0CD-4BA7-B4A6-2837D0702079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -603,7 +603,7 @@
       <sheetData sheetId="2">
         <row r="12">
           <cell r="P12">
-            <v>324175</v>
+            <v>365867</v>
           </cell>
         </row>
       </sheetData>
@@ -613,14 +613,14 @@
             <v>500217</v>
           </cell>
           <cell r="W9">
-            <v>269750</v>
+            <v>304415</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="4">
         <row r="9">
           <cell r="L9">
-            <v>269750</v>
+            <v>304415</v>
           </cell>
         </row>
       </sheetData>
@@ -631,7 +631,7 @@
             <v>44970</v>
           </cell>
           <cell r="L7">
-            <v>24242</v>
+            <v>25196</v>
           </cell>
         </row>
       </sheetData>
@@ -726,21 +726,21 @@
             <v>239872</v>
           </cell>
           <cell r="L18">
-            <v>108766</v>
+            <v>127484</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="10">
         <row r="11">
           <cell r="L11">
-            <v>25716</v>
+            <v>26446</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="11">
         <row r="13">
           <cell r="L13">
-            <v>25744</v>
+            <v>31787</v>
           </cell>
         </row>
       </sheetData>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Total Unidades Mensuales'!$P$12</f>
-        <v>324175</v>
+        <v>365867</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="H4" s="3">
         <f>(H3-G3)/G3</f>
-        <v>-0.43949367263698624</v>
+        <v>-0.36740720760908846</v>
       </c>
     </row>
   </sheetData>
@@ -1301,7 +1301,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]Gelatina!$L$13</f>
-        <v>25744</v>
+        <v>31787</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.27097669413530429</v>
+        <v>-9.9849913629541528E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Total Cremigurt Unidades'!$W$9</f>
-        <v>269750</v>
+        <v>304415</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-0.46073404142602109</v>
+        <v>-0.39143411759296465</v>
       </c>
     </row>
   </sheetData>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]150 gr'!$L$9</f>
-        <v>269750</v>
+        <v>304415</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-0.3839945923973857</v>
+        <v>-0.30483304483651591</v>
       </c>
     </row>
   </sheetData>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]700 gr'!$L$7</f>
-        <v>24242</v>
+        <v>25196</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-0.46092950856126308</v>
+        <v>-0.43971536579942183</v>
       </c>
     </row>
   </sheetData>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]Frutas!$L$18</f>
-        <v>108766</v>
+        <v>127484</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.54656650213447167</v>
+        <v>-0.46853321771611528</v>
       </c>
     </row>
   </sheetData>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]Cremosillo!$L$11</f>
-        <v>25716</v>
+        <v>26446</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.31284737067122703</v>
+        <v>-0.29334117144078664</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico_Produccion_CREMIGURT.xlsx
+++ b/data/Historico_Produccion_CREMIGURT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1165E0F-A0CD-4BA7-B4A6-2837D0702079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F5F6C32-C4F4-4640-A25F-CC47C2C31962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -598,12 +598,12 @@
       <sheetName val="Gelatina"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
       <sheetData sheetId="2">
         <row r="12">
           <cell r="P12">
-            <v>365867</v>
+            <v>383958</v>
           </cell>
         </row>
       </sheetData>
@@ -613,25 +613,25 @@
             <v>500217</v>
           </cell>
           <cell r="W9">
-            <v>304415</v>
+            <v>317725</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="4">
         <row r="9">
           <cell r="L9">
-            <v>304415</v>
+            <v>317725</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="5"/>
+      <sheetData sheetId="5" refreshError="1"/>
       <sheetData sheetId="6">
         <row r="7">
           <cell r="K7">
             <v>44970</v>
           </cell>
           <cell r="L7">
-            <v>25196</v>
+            <v>28071</v>
           </cell>
         </row>
       </sheetData>
@@ -653,7 +653,7 @@
         </row>
         <row r="7">
           <cell r="J7">
-            <v>1292</v>
+            <v>1759</v>
           </cell>
         </row>
         <row r="8">
@@ -661,12 +661,12 @@
             <v>24605</v>
           </cell>
           <cell r="J8">
-            <v>20043</v>
+            <v>21555</v>
           </cell>
         </row>
         <row r="9">
           <cell r="J9">
-            <v>1826</v>
+            <v>2475</v>
           </cell>
         </row>
         <row r="10">
@@ -674,7 +674,7 @@
             <v>12002</v>
           </cell>
           <cell r="J10">
-            <v>3915</v>
+            <v>6133</v>
           </cell>
         </row>
         <row r="11">
@@ -682,7 +682,7 @@
             <v>12086</v>
           </cell>
           <cell r="J11">
-            <v>1931</v>
+            <v>3596</v>
           </cell>
         </row>
         <row r="12">
@@ -726,14 +726,14 @@
             <v>239872</v>
           </cell>
           <cell r="L18">
-            <v>127484</v>
+            <v>131859</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="10">
         <row r="11">
           <cell r="L11">
-            <v>26446</v>
+            <v>30715</v>
           </cell>
         </row>
       </sheetData>
@@ -775,7 +775,7 @@
       <sheetName val="RESUMEN COP BY SKU"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
+      <sheetData sheetId="0" refreshError="1"/>
       <sheetData sheetId="1">
         <row r="4">
           <cell r="D4">
@@ -783,39 +783,27 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2">
-        <row r="24">
-          <cell r="C24">
-            <v>76012</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8">
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1">
         <row r="88">
           <cell r="AD88">
             <v>437902</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10">
-        <row r="39">
-          <cell r="G39">
-            <v>60829</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1188,7 +1176,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Total Unidades Mensuales'!$P$12</f>
-        <v>365867</v>
+        <v>383958</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1218,7 +1206,7 @@
       </c>
       <c r="H4" s="3">
         <f>(H3-G3)/G3</f>
-        <v>-0.36740720760908846</v>
+        <v>-0.33612743597856704</v>
       </c>
     </row>
   </sheetData>
@@ -1415,7 +1403,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Total Cremigurt Unidades'!$W$9</f>
-        <v>304415</v>
+        <v>317725</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1449,7 +1437,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-0.39143411759296465</v>
+        <v>-0.36482566566110308</v>
       </c>
     </row>
   </sheetData>
@@ -1532,7 +1520,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]150 gr'!$L$9</f>
-        <v>304415</v>
+        <v>317725</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1563,7 +1551,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-0.30483304483651591</v>
+        <v>-0.27443811629085962</v>
       </c>
     </row>
   </sheetData>
@@ -1646,7 +1634,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]700 gr'!$L$7</f>
-        <v>25196</v>
+        <v>28071</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1677,7 +1665,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-0.43971536579942183</v>
+        <v>-0.37578385590393598</v>
       </c>
     </row>
   </sheetData>
@@ -1870,7 +1858,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]POWER!$J$6+[2]POWER!$J$8+[2]POWER!$J$10+[2]POWER!$J$11+[2]POWER!$J$12+[2]POWER!$J$13</f>
-        <v>46509</v>
+        <v>51904</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1901,7 +1889,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.41669070522870078</v>
+        <v>-0.34902737887700197</v>
       </c>
     </row>
   </sheetData>
@@ -1984,7 +1972,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]POWER!$J$7+[2]POWER!$J$9</f>
-        <v>3118</v>
+        <v>4234</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2015,7 +2003,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.48860095128751846</v>
+        <v>-0.3055601115302608</v>
       </c>
     </row>
   </sheetData>
@@ -2098,7 +2086,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]Frutas!$L$18</f>
-        <v>127484</v>
+        <v>131859</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2129,7 +2117,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.46853321771611528</v>
+        <v>-0.4502943236392743</v>
       </c>
     </row>
   </sheetData>
@@ -2212,7 +2200,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]Cremosillo!$L$11</f>
-        <v>26446</v>
+        <v>30715</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2243,7 +2231,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.29334117144078664</v>
+        <v>-0.179269987174006</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico_Produccion_CREMIGURT.xlsx
+++ b/data/Historico_Produccion_CREMIGURT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F5F6C32-C4F4-4640-A25F-CC47C2C31962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CF496EE-04B8-4CEC-BB4F-03D1D93273B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -598,12 +598,12 @@
       <sheetName val="Gelatina"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
       <sheetData sheetId="2">
         <row r="12">
           <cell r="P12">
-            <v>383958</v>
+            <v>415654</v>
           </cell>
         </row>
       </sheetData>
@@ -613,32 +613,32 @@
             <v>500217</v>
           </cell>
           <cell r="W9">
-            <v>317725</v>
+            <v>349042</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="4">
         <row r="9">
           <cell r="L9">
-            <v>317725</v>
+            <v>349042</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="5"/>
       <sheetData sheetId="6">
         <row r="7">
           <cell r="K7">
             <v>44970</v>
           </cell>
           <cell r="L7">
-            <v>28071</v>
+            <v>30264</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="7">
         <row r="10">
           <cell r="K10">
-            <v>30119</v>
+            <v>31739</v>
           </cell>
         </row>
       </sheetData>
@@ -661,7 +661,7 @@
             <v>24605</v>
           </cell>
           <cell r="J8">
-            <v>21555</v>
+            <v>22290</v>
           </cell>
         </row>
         <row r="9">
@@ -726,7 +726,7 @@
             <v>239872</v>
           </cell>
           <cell r="L18">
-            <v>131859</v>
+            <v>145636</v>
           </cell>
         </row>
       </sheetData>
@@ -775,7 +775,7 @@
       <sheetName val="RESUMEN COP BY SKU"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="0"/>
       <sheetData sheetId="1">
         <row r="4">
           <cell r="D4">
@@ -783,27 +783,33 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1">
+      <sheetData sheetId="2">
+        <row r="24">
+          <cell r="C24">
+            <v>76012</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8">
         <row r="88">
           <cell r="AD88">
             <v>437902</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1176,7 +1182,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Total Unidades Mensuales'!$P$12</f>
-        <v>383958</v>
+        <v>415654</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1206,7 +1212,7 @@
       </c>
       <c r="H4" s="3">
         <f>(H3-G3)/G3</f>
-        <v>-0.33612743597856704</v>
+        <v>-0.28132429399631026</v>
       </c>
     </row>
   </sheetData>
@@ -1403,7 +1409,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Total Cremigurt Unidades'!$W$9</f>
-        <v>317725</v>
+        <v>349042</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1437,7 +1443,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-0.36482566566110308</v>
+        <v>-0.30221883702473129</v>
       </c>
     </row>
   </sheetData>
@@ -1520,7 +1526,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]150 gr'!$L$9</f>
-        <v>317725</v>
+        <v>349042</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1551,7 +1557,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-0.27443811629085962</v>
+        <v>-0.20292211499376572</v>
       </c>
     </row>
   </sheetData>
@@ -1634,7 +1640,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]700 gr'!$L$7</f>
-        <v>28071</v>
+        <v>30264</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1665,7 +1671,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-0.37578385590393598</v>
+        <v>-0.32701801200800534</v>
       </c>
     </row>
   </sheetData>
@@ -1747,7 +1753,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Linea Azul'!$K$10</f>
-        <v>30119</v>
+        <v>31739</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1775,7 +1781,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.49805849512540623</v>
+        <v>-0.47106074493792183</v>
       </c>
     </row>
   </sheetData>
@@ -1858,7 +1864,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]POWER!$J$6+[2]POWER!$J$8+[2]POWER!$J$10+[2]POWER!$J$11+[2]POWER!$J$12+[2]POWER!$J$13</f>
-        <v>51904</v>
+        <v>52639</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1889,7 +1895,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.34902737887700197</v>
+        <v>-0.33980911291435167</v>
       </c>
     </row>
   </sheetData>
@@ -2086,7 +2092,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]Frutas!$L$18</f>
-        <v>131859</v>
+        <v>145636</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2117,7 +2123,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.4502943236392743</v>
+        <v>-0.39285952508004268</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico_Produccion_CREMIGURT.xlsx
+++ b/data/Historico_Produccion_CREMIGURT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CF496EE-04B8-4CEC-BB4F-03D1D93273B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6445E985-4315-4F72-B0A4-B5D9F2DCD2D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -603,7 +603,7 @@
       <sheetData sheetId="2">
         <row r="12">
           <cell r="P12">
-            <v>415654</v>
+            <v>456855</v>
           </cell>
         </row>
       </sheetData>
@@ -613,14 +613,14 @@
             <v>500217</v>
           </cell>
           <cell r="W9">
-            <v>349042</v>
+            <v>387503</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="4">
         <row r="9">
           <cell r="L9">
-            <v>349042</v>
+            <v>387503</v>
           </cell>
         </row>
       </sheetData>
@@ -631,14 +631,14 @@
             <v>44970</v>
           </cell>
           <cell r="L7">
-            <v>30264</v>
+            <v>32965</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="7">
         <row r="10">
           <cell r="K10">
-            <v>31739</v>
+            <v>40206</v>
           </cell>
         </row>
       </sheetData>
@@ -726,7 +726,7 @@
             <v>239872</v>
           </cell>
           <cell r="L18">
-            <v>145636</v>
+            <v>171436</v>
           </cell>
         </row>
       </sheetData>
@@ -740,7 +740,7 @@
       <sheetData sheetId="11">
         <row r="13">
           <cell r="L13">
-            <v>31787</v>
+            <v>34527</v>
           </cell>
         </row>
       </sheetData>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Total Unidades Mensuales'!$P$12</f>
-        <v>415654</v>
+        <v>456855</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="H4" s="3">
         <f>(H3-G3)/G3</f>
-        <v>-0.28132429399631026</v>
+        <v>-0.21008677971025017</v>
       </c>
     </row>
   </sheetData>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]Gelatina!$L$13</f>
-        <v>31787</v>
+        <v>34527</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-9.9849913629541528E-2</v>
+        <v>-2.225809192082236E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Total Cremigurt Unidades'!$W$9</f>
-        <v>349042</v>
+        <v>387503</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-0.30221883702473129</v>
+        <v>-0.22533020669029641</v>
       </c>
     </row>
   </sheetData>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]150 gr'!$L$9</f>
-        <v>349042</v>
+        <v>387503</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-0.20292211499376572</v>
+        <v>-0.11509196121506639</v>
       </c>
     </row>
   </sheetData>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]700 gr'!$L$7</f>
-        <v>30264</v>
+        <v>32965</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-0.32701801200800534</v>
+        <v>-0.26695574827662888</v>
       </c>
     </row>
   </sheetData>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Linea Azul'!$K$10</f>
-        <v>31739</v>
+        <v>40206</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.47106074493792183</v>
+        <v>-0.32995583701358222</v>
       </c>
     </row>
   </sheetData>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]Frutas!$L$18</f>
-        <v>145636</v>
+        <v>171436</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.39285952508004268</v>
+        <v>-0.28530216115261475</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico_Produccion_CREMIGURT.xlsx
+++ b/data/Historico_Produccion_CREMIGURT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6445E985-4315-4F72-B0A4-B5D9F2DCD2D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EEA8C6D-FF9E-4725-8DCA-C101913FDF6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -598,12 +598,12 @@
       <sheetName val="Gelatina"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
       <sheetData sheetId="2">
         <row r="12">
           <cell r="P12">
-            <v>456855</v>
+            <v>492923</v>
           </cell>
         </row>
       </sheetData>
@@ -613,25 +613,25 @@
             <v>500217</v>
           </cell>
           <cell r="W9">
-            <v>387503</v>
+            <v>417276</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="4">
         <row r="9">
           <cell r="L9">
-            <v>387503</v>
+            <v>417276</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="5"/>
+      <sheetData sheetId="5" refreshError="1"/>
       <sheetData sheetId="6">
         <row r="7">
           <cell r="K7">
             <v>44970</v>
           </cell>
           <cell r="L7">
-            <v>32965</v>
+            <v>35156</v>
           </cell>
         </row>
       </sheetData>
@@ -648,12 +648,12 @@
             <v>15181</v>
           </cell>
           <cell r="J6">
-            <v>12363</v>
+            <v>14331</v>
           </cell>
         </row>
         <row r="7">
           <cell r="J7">
-            <v>1759</v>
+            <v>2209</v>
           </cell>
         </row>
         <row r="8">
@@ -661,7 +661,7 @@
             <v>24605</v>
           </cell>
           <cell r="J8">
-            <v>22290</v>
+            <v>24366</v>
           </cell>
         </row>
         <row r="9">
@@ -674,7 +674,7 @@
             <v>12002</v>
           </cell>
           <cell r="J10">
-            <v>6133</v>
+            <v>8117</v>
           </cell>
         </row>
         <row r="11">
@@ -682,7 +682,7 @@
             <v>12086</v>
           </cell>
           <cell r="J11">
-            <v>3596</v>
+            <v>5635</v>
           </cell>
         </row>
         <row r="12">
@@ -726,21 +726,21 @@
             <v>239872</v>
           </cell>
           <cell r="L18">
-            <v>171436</v>
+            <v>187810</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="10">
         <row r="11">
           <cell r="L11">
-            <v>30715</v>
+            <v>32633</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="11">
         <row r="13">
           <cell r="L13">
-            <v>34527</v>
+            <v>38519</v>
           </cell>
         </row>
       </sheetData>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Total Unidades Mensuales'!$P$12</f>
-        <v>456855</v>
+        <v>492923</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="H4" s="3">
         <f>(H3-G3)/G3</f>
-        <v>-0.21008677971025017</v>
+        <v>-0.14772434517541813</v>
       </c>
     </row>
   </sheetData>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]Gelatina!$L$13</f>
-        <v>34527</v>
+        <v>38519</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-2.225809192082236E-2</v>
+        <v>9.0788095035822497E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Total Cremigurt Unidades'!$W$9</f>
-        <v>387503</v>
+        <v>417276</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-0.22533020669029641</v>
+        <v>-0.1658100384433156</v>
       </c>
     </row>
   </sheetData>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]150 gr'!$L$9</f>
-        <v>387503</v>
+        <v>417276</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-0.11509196121506639</v>
+        <v>-4.7101862973907407E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]700 gr'!$L$7</f>
-        <v>32965</v>
+        <v>35156</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-0.26695574827662888</v>
+        <v>-0.21823437847453858</v>
       </c>
     </row>
   </sheetData>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]POWER!$J$6+[2]POWER!$J$8+[2]POWER!$J$10+[2]POWER!$J$11+[2]POWER!$J$12+[2]POWER!$J$13</f>
-        <v>52639</v>
+        <v>60706</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.33980911291435167</v>
+        <v>-0.2386339407773444</v>
       </c>
     </row>
   </sheetData>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]POWER!$J$7+[2]POWER!$J$9</f>
-        <v>4234</v>
+        <v>4684</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.3055601115302608</v>
+        <v>-0.23175332130556012</v>
       </c>
     </row>
   </sheetData>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]Frutas!$L$18</f>
-        <v>171436</v>
+        <v>187810</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.28530216115261475</v>
+        <v>-0.21704075506937034</v>
       </c>
     </row>
   </sheetData>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]Cremosillo!$L$11</f>
-        <v>30715</v>
+        <v>32633</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.179269987174006</v>
+        <v>-0.12801945275758872</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico_Produccion_CREMIGURT.xlsx
+++ b/data/Historico_Produccion_CREMIGURT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EEA8C6D-FF9E-4725-8DCA-C101913FDF6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2AA62F9-753F-4249-A196-9E37352FF998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -598,12 +598,12 @@
       <sheetName val="Gelatina"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
       <sheetData sheetId="2">
         <row r="12">
           <cell r="P12">
-            <v>492923</v>
+            <v>526590</v>
           </cell>
         </row>
       </sheetData>
@@ -613,32 +613,32 @@
             <v>500217</v>
           </cell>
           <cell r="W9">
-            <v>417276</v>
+            <v>450943</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="4">
         <row r="9">
           <cell r="L9">
-            <v>417276</v>
+            <v>450943</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="5"/>
       <sheetData sheetId="6">
         <row r="7">
           <cell r="K7">
             <v>44970</v>
           </cell>
           <cell r="L7">
-            <v>35156</v>
+            <v>36486</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="7">
         <row r="10">
           <cell r="K10">
-            <v>40206</v>
+            <v>47807</v>
           </cell>
         </row>
       </sheetData>
@@ -661,12 +661,12 @@
             <v>24605</v>
           </cell>
           <cell r="J8">
-            <v>24366</v>
+            <v>26351</v>
           </cell>
         </row>
         <row r="9">
           <cell r="J9">
-            <v>2475</v>
+            <v>3353</v>
           </cell>
         </row>
         <row r="10">
@@ -726,7 +726,7 @@
             <v>239872</v>
           </cell>
           <cell r="L18">
-            <v>187810</v>
+            <v>199650</v>
           </cell>
         </row>
       </sheetData>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Total Unidades Mensuales'!$P$12</f>
-        <v>492923</v>
+        <v>526590</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="H4" s="3">
         <f>(H3-G3)/G3</f>
-        <v>-0.14772434517541813</v>
+        <v>-8.9513297058411614E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Total Cremigurt Unidades'!$W$9</f>
-        <v>417276</v>
+        <v>450943</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-0.1658100384433156</v>
+        <v>-9.8505248722054628E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]150 gr'!$L$9</f>
-        <v>417276</v>
+        <v>450943</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-4.7101862973907407E-2</v>
+        <v>2.9780635850030372E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]700 gr'!$L$7</f>
-        <v>35156</v>
+        <v>36486</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-0.21823437847453858</v>
+        <v>-0.18865910607071382</v>
       </c>
     </row>
   </sheetData>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Linea Azul'!$K$10</f>
-        <v>40206</v>
+        <v>47807</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.32995583701358222</v>
+        <v>-0.20328305974502126</v>
       </c>
     </row>
   </sheetData>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]POWER!$J$6+[2]POWER!$J$8+[2]POWER!$J$10+[2]POWER!$J$11+[2]POWER!$J$12+[2]POWER!$J$13</f>
-        <v>60706</v>
+        <v>62691</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.2386339407773444</v>
+        <v>-0.21373835174896216</v>
       </c>
     </row>
   </sheetData>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]POWER!$J$7+[2]POWER!$J$9</f>
-        <v>4684</v>
+        <v>5562</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.23175332130556012</v>
+        <v>-8.7748072822699683E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]Frutas!$L$18</f>
-        <v>187810</v>
+        <v>199650</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.21704075506937034</v>
+        <v>-0.16768109658484526</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico_Produccion_CREMIGURT.xlsx
+++ b/data/Historico_Produccion_CREMIGURT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2AA62F9-753F-4249-A196-9E37352FF998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A70B6BD2-E7A1-421B-AF2F-D9EDB2F1F970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -603,7 +603,7 @@
       <sheetData sheetId="2">
         <row r="12">
           <cell r="P12">
-            <v>526590</v>
+            <v>554410</v>
           </cell>
         </row>
       </sheetData>
@@ -613,14 +613,14 @@
             <v>500217</v>
           </cell>
           <cell r="W9">
-            <v>450943</v>
+            <v>469332</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="4">
         <row r="9">
           <cell r="L9">
-            <v>450943</v>
+            <v>469332</v>
           </cell>
         </row>
       </sheetData>
@@ -631,14 +631,14 @@
             <v>44970</v>
           </cell>
           <cell r="L7">
-            <v>36486</v>
+            <v>41994</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="7">
         <row r="10">
           <cell r="K10">
-            <v>47807</v>
+            <v>50269</v>
           </cell>
         </row>
       </sheetData>
@@ -726,14 +726,14 @@
             <v>239872</v>
           </cell>
           <cell r="L18">
-            <v>199650</v>
+            <v>210936</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="10">
         <row r="11">
           <cell r="L11">
-            <v>32633</v>
+            <v>42064</v>
           </cell>
         </row>
       </sheetData>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Total Unidades Mensuales'!$P$12</f>
-        <v>526590</v>
+        <v>554410</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="H4" s="3">
         <f>(H3-G3)/G3</f>
-        <v>-8.9513297058411614E-2</v>
+        <v>-4.1411851767321796E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Total Cremigurt Unidades'!$W$9</f>
-        <v>450943</v>
+        <v>469332</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-9.8505248722054628E-2</v>
+        <v>-6.1743203449702827E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]150 gr'!$L$9</f>
-        <v>450943</v>
+        <v>469332</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>2.9780635850030372E-2</v>
+        <v>7.1774049901576153E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]700 gr'!$L$7</f>
-        <v>36486</v>
+        <v>41994</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-0.18865910607071382</v>
+        <v>-6.6177451634422943E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Linea Azul'!$K$10</f>
-        <v>47807</v>
+        <v>50269</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.20328305974502126</v>
+        <v>-0.16225314557120241</v>
       </c>
     </row>
   </sheetData>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]Frutas!$L$18</f>
-        <v>199650</v>
+        <v>210936</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.16768109658484526</v>
+        <v>-0.12063100320170758</v>
       </c>
     </row>
   </sheetData>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]Cremosillo!$L$11</f>
-        <v>32633</v>
+        <v>42064</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.12801945275758872</v>
+        <v>0.12398460880718255</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico_Produccion_CREMIGURT.xlsx
+++ b/data/Historico_Produccion_CREMIGURT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A70B6BD2-E7A1-421B-AF2F-D9EDB2F1F970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C53759D6-755D-422D-BDA0-02EFBCFACE33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -603,7 +603,7 @@
       <sheetData sheetId="2">
         <row r="12">
           <cell r="P12">
-            <v>554410</v>
+            <v>581918</v>
           </cell>
         </row>
       </sheetData>
@@ -613,14 +613,14 @@
             <v>500217</v>
           </cell>
           <cell r="W9">
-            <v>469332</v>
+            <v>488460</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="4">
         <row r="9">
           <cell r="L9">
-            <v>469332</v>
+            <v>488460</v>
           </cell>
         </row>
       </sheetData>
@@ -631,7 +631,7 @@
             <v>44970</v>
           </cell>
           <cell r="L7">
-            <v>41994</v>
+            <v>45956</v>
           </cell>
         </row>
       </sheetData>
@@ -648,12 +648,12 @@
             <v>15181</v>
           </cell>
           <cell r="J6">
-            <v>14331</v>
+            <v>16246</v>
           </cell>
         </row>
         <row r="7">
           <cell r="J7">
-            <v>2209</v>
+            <v>2616</v>
           </cell>
         </row>
         <row r="8">
@@ -666,7 +666,7 @@
         </row>
         <row r="9">
           <cell r="J9">
-            <v>3353</v>
+            <v>5351</v>
           </cell>
         </row>
         <row r="10">
@@ -682,7 +682,7 @@
             <v>12086</v>
           </cell>
           <cell r="J11">
-            <v>5635</v>
+            <v>8830</v>
           </cell>
         </row>
         <row r="12">
@@ -726,21 +726,21 @@
             <v>239872</v>
           </cell>
           <cell r="L18">
-            <v>210936</v>
+            <v>222529</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="10">
         <row r="11">
           <cell r="L11">
-            <v>42064</v>
+            <v>42782</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="11">
         <row r="13">
           <cell r="L13">
-            <v>38519</v>
+            <v>43423</v>
           </cell>
         </row>
       </sheetData>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Total Unidades Mensuales'!$P$12</f>
-        <v>554410</v>
+        <v>581918</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="H4" s="3">
         <f>(H3-G3)/G3</f>
-        <v>-4.1411851767321796E-2</v>
+        <v>6.1501380625595429E-3</v>
       </c>
     </row>
   </sheetData>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]Gelatina!$L$13</f>
-        <v>38519</v>
+        <v>43423</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>9.0788095035822497E-2</v>
+        <v>0.2296604649845666</v>
       </c>
     </row>
   </sheetData>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Total Cremigurt Unidades'!$W$9</f>
-        <v>469332</v>
+        <v>488460</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-6.1743203449702827E-2</v>
+        <v>-2.3503799351081631E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]150 gr'!$L$9</f>
-        <v>469332</v>
+        <v>488460</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>7.1774049901576153E-2</v>
+        <v>0.11545505615411668</v>
       </c>
     </row>
   </sheetData>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]700 gr'!$L$7</f>
-        <v>41994</v>
+        <v>45956</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-6.6177451634422943E-2</v>
+        <v>2.1925728263286634E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]POWER!$J$6+[2]POWER!$J$8+[2]POWER!$J$10+[2]POWER!$J$11+[2]POWER!$J$12+[2]POWER!$J$13</f>
-        <v>62691</v>
+        <v>67801</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.21373835174896216</v>
+        <v>-0.14964945505625024</v>
       </c>
     </row>
   </sheetData>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]POWER!$J$7+[2]POWER!$J$9</f>
-        <v>5562</v>
+        <v>7967</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-8.7748072822699683E-2</v>
+        <v>0.30670821715597835</v>
       </c>
     </row>
   </sheetData>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]Frutas!$L$18</f>
-        <v>210936</v>
+        <v>222529</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.12063100320170758</v>
+        <v>-7.2301060565635011E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]Cremosillo!$L$11</f>
-        <v>42064</v>
+        <v>42782</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>0.12398460880718255</v>
+        <v>0.14317015818725951</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico_Produccion_CREMIGURT.xlsx
+++ b/data/Historico_Produccion_CREMIGURT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C53759D6-755D-422D-BDA0-02EFBCFACE33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{083A8486-159D-4529-A753-258B8BA49428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -598,12 +598,12 @@
       <sheetName val="Gelatina"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
       <sheetData sheetId="2">
         <row r="12">
           <cell r="P12">
-            <v>581918</v>
+            <v>617152</v>
           </cell>
         </row>
       </sheetData>
@@ -613,32 +613,32 @@
             <v>500217</v>
           </cell>
           <cell r="W9">
-            <v>488460</v>
+            <v>517664</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="4">
         <row r="9">
           <cell r="L9">
-            <v>488460</v>
+            <v>445754</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="5"/>
+      <sheetData sheetId="5" refreshError="1"/>
       <sheetData sheetId="6">
         <row r="7">
           <cell r="K7">
             <v>44970</v>
           </cell>
           <cell r="L7">
-            <v>45956</v>
+            <v>47151</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="7">
         <row r="10">
           <cell r="K10">
-            <v>50269</v>
+            <v>65487</v>
           </cell>
         </row>
       </sheetData>
@@ -661,12 +661,12 @@
             <v>24605</v>
           </cell>
           <cell r="J8">
-            <v>26351</v>
+            <v>28349</v>
           </cell>
         </row>
         <row r="9">
           <cell r="J9">
-            <v>5351</v>
+            <v>3353</v>
           </cell>
         </row>
         <row r="10">
@@ -674,7 +674,7 @@
             <v>12002</v>
           </cell>
           <cell r="J10">
-            <v>8117</v>
+            <v>11277</v>
           </cell>
         </row>
         <row r="11">
@@ -740,7 +740,7 @@
       <sheetData sheetId="11">
         <row r="13">
           <cell r="L13">
-            <v>43423</v>
+            <v>52211</v>
           </cell>
         </row>
       </sheetData>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Total Unidades Mensuales'!$P$12</f>
-        <v>581918</v>
+        <v>617152</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="H4" s="3">
         <f>(H3-G3)/G3</f>
-        <v>6.1501380625595429E-3</v>
+        <v>6.7070566653007382E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]Gelatina!$L$13</f>
-        <v>43423</v>
+        <v>52211</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>0.2296604649845666</v>
+        <v>0.47852065811457539</v>
       </c>
     </row>
   </sheetData>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Total Cremigurt Unidades'!$W$9</f>
-        <v>488460</v>
+        <v>517664</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>-2.3503799351081631E-2</v>
+        <v>3.4878862573643039E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]150 gr'!$L$9</f>
-        <v>488460</v>
+        <v>445754</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>0.11545505615411668</v>
+        <v>1.7930952587565253E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]700 gr'!$L$7</f>
-        <v>45956</v>
+        <v>47151</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>2.1925728263286634E-2</v>
+        <v>4.8498999332888593E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Linea Azul'!$K$10</f>
-        <v>50269</v>
+        <v>65487</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.16225314557120241</v>
+        <v>9.1359053412215646E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]POWER!$J$6+[2]POWER!$J$8+[2]POWER!$J$10+[2]POWER!$J$11+[2]POWER!$J$12+[2]POWER!$J$13</f>
-        <v>67801</v>
+        <v>72959</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-0.14964945505625024</v>
+        <v>-8.49585491578142E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]POWER!$J$7+[2]POWER!$J$9</f>
-        <v>7967</v>
+        <v>5969</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>0.30670821715597835</v>
+        <v>-2.0993931441692634E-2</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico_Produccion_CREMIGURT.xlsx
+++ b/data/Historico_Produccion_CREMIGURT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{083A8486-159D-4529-A753-258B8BA49428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67258830-D0B4-4C12-AA66-4B3DC77553D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -598,12 +598,12 @@
       <sheetName val="Gelatina"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
       <sheetData sheetId="2">
         <row r="12">
           <cell r="P12">
-            <v>617152</v>
+            <v>658622</v>
           </cell>
         </row>
       </sheetData>
@@ -613,32 +613,32 @@
             <v>500217</v>
           </cell>
           <cell r="W9">
-            <v>517664</v>
+            <v>547913</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="4">
         <row r="9">
           <cell r="L9">
-            <v>445754</v>
+            <v>474433</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="5"/>
       <sheetData sheetId="6">
         <row r="7">
           <cell r="K7">
             <v>44970</v>
           </cell>
           <cell r="L7">
-            <v>47151</v>
+            <v>48706</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="7">
         <row r="10">
           <cell r="K10">
-            <v>65487</v>
+            <v>70627</v>
           </cell>
         </row>
       </sheetData>
@@ -648,7 +648,7 @@
             <v>15181</v>
           </cell>
           <cell r="J6">
-            <v>16246</v>
+            <v>19404</v>
           </cell>
         </row>
         <row r="7">
@@ -661,7 +661,7 @@
             <v>24605</v>
           </cell>
           <cell r="J8">
-            <v>28349</v>
+            <v>31637</v>
           </cell>
         </row>
         <row r="9">
@@ -726,21 +726,21 @@
             <v>239872</v>
           </cell>
           <cell r="L18">
-            <v>222529</v>
+            <v>239181</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="10">
         <row r="11">
           <cell r="L11">
-            <v>42782</v>
+            <v>52480</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="11">
         <row r="13">
           <cell r="L13">
-            <v>52211</v>
+            <v>53734</v>
           </cell>
         </row>
       </sheetData>
@@ -1182,7 +1182,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Total Unidades Mensuales'!$P$12</f>
-        <v>617152</v>
+        <v>658622</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="H4" s="3">
         <f>(H3-G3)/G3</f>
-        <v>6.7070566653007382E-2</v>
+        <v>0.13877318837196836</v>
       </c>
     </row>
   </sheetData>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]Gelatina!$L$13</f>
-        <v>52211</v>
+        <v>53734</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>0.47852065811457539</v>
+        <v>0.5216492509840569</v>
       </c>
     </row>
   </sheetData>
@@ -1409,7 +1409,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Total Cremigurt Unidades'!$W$9</f>
-        <v>517664</v>
+        <v>547913</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>3.4878862573643039E-2</v>
+        <v>9.5350617831860968E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]150 gr'!$L$9</f>
-        <v>445754</v>
+        <v>474433</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>1.7930952587565253E-2</v>
+        <v>8.3422774958780727E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]700 gr'!$L$7</f>
-        <v>47151</v>
+        <v>48706</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>4.8498999332888593E-2</v>
+        <v>8.3077607293751396E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Linea Azul'!$K$10</f>
-        <v>65487</v>
+        <v>70627</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>9.1359053412215646E-2</v>
+        <v>0.17701858178485128</v>
       </c>
     </row>
   </sheetData>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]POWER!$J$6+[2]POWER!$J$8+[2]POWER!$J$10+[2]POWER!$J$11+[2]POWER!$J$12+[2]POWER!$J$13</f>
-        <v>72959</v>
+        <v>79405</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-8.49585491578142E-2</v>
+        <v>-4.1137295724480456E-3</v>
       </c>
     </row>
   </sheetData>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]Frutas!$L$18</f>
-        <v>222529</v>
+        <v>239181</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-7.2301060565635011E-2</v>
+        <v>-2.8807030416221984E-3</v>
       </c>
     </row>
   </sheetData>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]Cremosillo!$L$11</f>
-        <v>42782</v>
+        <v>52480</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>0.14317015818725951</v>
+        <v>0.40230867892261651</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico_Produccion_CREMIGURT.xlsx
+++ b/data/Historico_Produccion_CREMIGURT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67258830-D0B4-4C12-AA66-4B3DC77553D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC058443-C4E9-4EE1-87D9-6E3C0474E229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -602,8 +602,14 @@
       <sheetData sheetId="1"/>
       <sheetData sheetId="2">
         <row r="12">
+          <cell r="O12">
+            <v>578361</v>
+          </cell>
           <cell r="P12">
-            <v>658622</v>
+            <v>687903</v>
+          </cell>
+          <cell r="Q12">
+            <v>17207</v>
           </cell>
         </row>
       </sheetData>
@@ -613,14 +619,20 @@
             <v>500217</v>
           </cell>
           <cell r="W9">
-            <v>547913</v>
+            <v>577194</v>
+          </cell>
+          <cell r="X9">
+            <v>16432</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="4">
         <row r="9">
           <cell r="L9">
-            <v>474433</v>
+            <v>498292</v>
+          </cell>
+          <cell r="M9">
+            <v>11516</v>
           </cell>
         </row>
       </sheetData>
@@ -631,7 +643,10 @@
             <v>44970</v>
           </cell>
           <cell r="L7">
-            <v>48706</v>
+            <v>54128</v>
+          </cell>
+          <cell r="M7">
+            <v>1061</v>
           </cell>
         </row>
       </sheetData>
@@ -653,7 +668,7 @@
         </row>
         <row r="7">
           <cell r="J7">
-            <v>2616</v>
+            <v>3221</v>
           </cell>
         </row>
         <row r="8">
@@ -666,7 +681,7 @@
         </row>
         <row r="9">
           <cell r="J9">
-            <v>3353</v>
+            <v>3881</v>
           </cell>
         </row>
         <row r="10">
@@ -726,7 +741,7 @@
             <v>239872</v>
           </cell>
           <cell r="L18">
-            <v>239181</v>
+            <v>253860</v>
           </cell>
         </row>
       </sheetData>
@@ -1112,10 +1127,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76A50725-B085-4570-857C-BD64735FAA95}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -1125,7 +1140,7 @@
       <c r="E1" s="12"/>
       <c r="F1" s="12"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46054</v>
       </c>
@@ -1150,8 +1165,11 @@
       <c r="H2" s="8">
         <v>46266</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="5">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <f>'[1]Total Unidades Mensuales'!I12</f>
         <v>520938</v>
@@ -1177,15 +1195,19 @@
         <v>518837</v>
       </c>
       <c r="G3" s="9">
-        <f>'[1]Sapori Pruccion Mensual'!$J$12</f>
+        <f>'[2]Total Unidades Mensuales'!$O$12</f>
         <v>578361</v>
       </c>
       <c r="H3" s="2">
         <f>'[2]Total Unidades Mensuales'!$P$12</f>
-        <v>658622</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <v>687903</v>
+      </c>
+      <c r="I3" s="2">
+        <f>'[2]Total Unidades Mensuales'!$Q$12</f>
+        <v>17207</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B4" s="3">
         <f>'[1]Total Unidades Mensuales'!J13</f>
         <v>-0.2070323147860206</v>
@@ -1212,7 +1234,11 @@
       </c>
       <c r="H4" s="3">
         <f>(H3-G3)/G3</f>
-        <v>0.13877318837196836</v>
+        <v>0.18940073760160175</v>
+      </c>
+      <c r="I4" s="3">
+        <f>(I3-H3)/H3</f>
+        <v>-0.9749862989404029</v>
       </c>
     </row>
   </sheetData>
@@ -1339,10 +1365,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{921C7DED-5639-47E9-9129-9ED451DB0330}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>1</v>
       </c>
@@ -1352,7 +1378,7 @@
       <c r="E1" s="12"/>
       <c r="F1" s="12"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46054</v>
       </c>
@@ -1377,8 +1403,11 @@
       <c r="H2" s="5">
         <v>46266</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="5">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>'[1]Total Cremigurt Unidades'!P9</f>
         <v>466290</v>
@@ -1409,10 +1438,14 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]Total Cremigurt Unidades'!$W$9</f>
-        <v>547913</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <v>577194</v>
+      </c>
+      <c r="I3">
+        <f>'[2]Total Cremigurt Unidades'!$X$9</f>
+        <v>16432</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <f>'[1]Total Cremigurt Unidades'!P10</f>
         <v>0.47828650777044379</v>
@@ -1443,7 +1476,11 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>9.5350617831860968E-2</v>
+        <v>0.15388721294957988</v>
+      </c>
+      <c r="I4" s="7">
+        <f>(I3-H3)/H3</f>
+        <v>-0.97153123559842969</v>
       </c>
     </row>
   </sheetData>
@@ -1456,10 +1493,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53811579-B0AE-4BBF-B8B9-801ECC475242}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>2</v>
       </c>
@@ -1469,7 +1506,7 @@
       <c r="E1" s="12"/>
       <c r="F1" s="12"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46054</v>
       </c>
@@ -1494,8 +1531,11 @@
       <c r="H2" s="5">
         <v>46266</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="5">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>'[1]150 gr'!E9</f>
         <v>386904</v>
@@ -1526,10 +1566,14 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]150 gr'!$L$9</f>
-        <v>474433</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <v>498292</v>
+      </c>
+      <c r="I3" s="2">
+        <f>'[2]150 gr'!$M$9</f>
+        <v>11516</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3">
         <f>'[1]150 gr'!F7</f>
@@ -1557,7 +1601,11 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>8.3422774958780727E-2</v>
+        <v>0.13790756836004403</v>
+      </c>
+      <c r="I4" s="7">
+        <f>(I3-H3)/H3</f>
+        <v>-0.97688905300506534</v>
       </c>
     </row>
   </sheetData>
@@ -1570,10 +1618,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F86516D-CC49-45A3-8161-FD9764305B52}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>3</v>
       </c>
@@ -1583,7 +1631,7 @@
       <c r="E1" s="12"/>
       <c r="F1" s="12"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46054</v>
       </c>
@@ -1608,8 +1656,11 @@
       <c r="H2" s="5">
         <v>46266</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="5">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <f>'[1]700 gr'!E7</f>
         <v>43534</v>
@@ -1640,10 +1691,14 @@
       </c>
       <c r="H3" s="2">
         <f>'[2]700 gr'!$L$7</f>
-        <v>48706</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <v>54128</v>
+      </c>
+      <c r="I3" s="2">
+        <f>'[2]700 gr'!$M$7</f>
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3">
         <f>'[1]700 gr'!F5</f>
@@ -1671,7 +1726,11 @@
       </c>
       <c r="H4" s="7">
         <f>(H3-G3)/G3</f>
-        <v>8.3077607293751396E-2</v>
+        <v>0.20364687569490772</v>
+      </c>
+      <c r="I4" s="7">
+        <f>(I3-H3)/H3</f>
+        <v>-0.98039831510493647</v>
       </c>
     </row>
   </sheetData>
@@ -1978,7 +2037,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]POWER!$J$7+[2]POWER!$J$9</f>
-        <v>5969</v>
+        <v>7102</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2009,7 +2068,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-2.0993931441692634E-2</v>
+        <v>0.16483516483516483</v>
       </c>
     </row>
   </sheetData>
@@ -2092,7 +2151,7 @@
       </c>
       <c r="H3" s="2">
         <f>[2]Frutas!$L$18</f>
-        <v>239181</v>
+        <v>253860</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -2123,7 +2182,7 @@
       </c>
       <c r="H4" s="4">
         <f t="shared" si="0"/>
-        <v>-2.8807030416221984E-3</v>
+        <v>5.8314434364994665E-2</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico_Produccion_CREMIGURT.xlsx
+++ b/data/Historico_Produccion_CREMIGURT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC058443-C4E9-4EE1-87D9-6E3C0474E229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58BC8EF1-10BF-4DFD-8EA0-3AA48EBB5789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -609,7 +609,7 @@
             <v>687903</v>
           </cell>
           <cell r="Q12">
-            <v>17207</v>
+            <v>31326</v>
           </cell>
         </row>
       </sheetData>
@@ -622,7 +622,7 @@
             <v>577194</v>
           </cell>
           <cell r="X9">
-            <v>16432</v>
+            <v>29574</v>
           </cell>
         </row>
       </sheetData>
@@ -632,7 +632,7 @@
             <v>498292</v>
           </cell>
           <cell r="M9">
-            <v>11516</v>
+            <v>23624</v>
           </cell>
         </row>
       </sheetData>
@@ -646,7 +646,7 @@
             <v>54128</v>
           </cell>
           <cell r="M7">
-            <v>1061</v>
+            <v>2095</v>
           </cell>
         </row>
       </sheetData>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I3" s="2">
         <f>'[2]Total Unidades Mensuales'!$Q$12</f>
-        <v>17207</v>
+        <v>31326</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="I4" s="3">
         <f>(I3-H3)/H3</f>
-        <v>-0.9749862989404029</v>
+        <v>-0.95446160287133508</v>
       </c>
     </row>
   </sheetData>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="I3">
         <f>'[2]Total Cremigurt Unidades'!$X$9</f>
-        <v>16432</v>
+        <v>29574</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="I4" s="7">
         <f>(I3-H3)/H3</f>
-        <v>-0.97153123559842969</v>
+        <v>-0.94876246114824481</v>
       </c>
     </row>
   </sheetData>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="I3" s="2">
         <f>'[2]150 gr'!$M$9</f>
-        <v>11516</v>
+        <v>23624</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="I4" s="7">
         <f>(I3-H3)/H3</f>
-        <v>-0.97688905300506534</v>
+        <v>-0.95259004760261057</v>
       </c>
     </row>
   </sheetData>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="I3" s="2">
         <f>'[2]700 gr'!$M$7</f>
-        <v>1061</v>
+        <v>2095</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="I4" s="7">
         <f>(I3-H3)/H3</f>
-        <v>-0.98039831510493647</v>
+        <v>-0.9612954478273722</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico_Produccion_CREMIGURT.xlsx
+++ b/data/Historico_Produccion_CREMIGURT.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr updateLinks="always" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Almacén\Mi_Dashboard_Ventas\dashboard_supply_v.2.0\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\SUPPLY CHAIN\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58BC8EF1-10BF-4DFD-8EA0-3AA48EBB5789}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5237397-39DC-4610-B4B4-E3FE9FAD8587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -26,8 +26,6 @@
   </sheets>
   <externalReferences>
     <externalReference r:id="rId11"/>
-    <externalReference r:id="rId12"/>
-    <externalReference r:id="rId13"/>
   </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
@@ -184,404 +182,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Sapori Pruccion Mensual"/>
-      <sheetName val="Comparativo vs Forecast"/>
-      <sheetName val="Total Unidades Mensuales"/>
-      <sheetName val="Total Cremigurt Unidades"/>
-      <sheetName val="150 gr"/>
-      <sheetName val="Hoja3"/>
-      <sheetName val="700 gr"/>
-      <sheetName val="Linea Azul"/>
-      <sheetName val="POWER"/>
-      <sheetName val="Frutas"/>
-      <sheetName val="Cremosillo"/>
-      <sheetName val="Gelatina"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="12">
-          <cell r="J12">
-            <v>578361</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2">
-        <row r="12">
-          <cell r="I12">
-            <v>520938</v>
-          </cell>
-          <cell r="J12">
-            <v>413087</v>
-          </cell>
-          <cell r="K12">
-            <v>535420</v>
-          </cell>
-          <cell r="L12">
-            <v>564513</v>
-          </cell>
-          <cell r="M12">
-            <v>609205</v>
-          </cell>
-          <cell r="N12">
-            <v>518837</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="J13">
-            <v>-0.2070323147860206</v>
-          </cell>
-          <cell r="K13">
-            <v>0.29614342741359567</v>
-          </cell>
-          <cell r="L13">
-            <v>5.4336782339098277E-2</v>
-          </cell>
-          <cell r="M13">
-            <v>7.9169124537433147E-2</v>
-          </cell>
-          <cell r="N13">
-            <v>-0.14833758751159298</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="3">
-        <row r="9">
-          <cell r="P9">
-            <v>466290</v>
-          </cell>
-          <cell r="Q9">
-            <v>321987</v>
-          </cell>
-          <cell r="R9">
-            <v>445909</v>
-          </cell>
-          <cell r="S9">
-            <v>449661</v>
-          </cell>
-          <cell r="T9">
-            <v>518112</v>
-          </cell>
-          <cell r="U9">
-            <v>429574</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="P10">
-            <v>0.47828650777044379</v>
-          </cell>
-          <cell r="Q10">
-            <v>-0.30947050119024644</v>
-          </cell>
-          <cell r="R10">
-            <v>0.38486646976430727</v>
-          </cell>
-          <cell r="S10">
-            <v>8.4142728673339186E-3</v>
-          </cell>
-          <cell r="T10">
-            <v>0.15222801176886588</v>
-          </cell>
-          <cell r="U10">
-            <v>-0.17088583163485888</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="4">
-        <row r="7">
-          <cell r="F7">
-            <v>-0.31414769555238509</v>
-          </cell>
-          <cell r="G7">
-            <v>0.45670958965024738</v>
-          </cell>
-          <cell r="H7">
-            <v>-7.0805663418281161E-3</v>
-          </cell>
-          <cell r="I7">
-            <v>0.20193635458842044</v>
-          </cell>
-          <cell r="J7">
-            <v>-0.22600580941645712</v>
-          </cell>
-          <cell r="K7">
-            <v>0.22641356190433515</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="E9">
-            <v>386904</v>
-          </cell>
-          <cell r="F9">
-            <v>265359</v>
-          </cell>
-          <cell r="G9">
-            <v>386551</v>
-          </cell>
-          <cell r="H9">
-            <v>383814</v>
-          </cell>
-          <cell r="I9">
-            <v>461320</v>
-          </cell>
-          <cell r="J9">
-            <v>357059</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6">
-        <row r="5">
-          <cell r="I5">
-            <v>-0.37216510723499285</v>
-          </cell>
-          <cell r="J5">
-            <v>0.38922449480236732</v>
-          </cell>
-          <cell r="K5">
-            <v>-7.372417446583083E-3</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="E7">
-            <v>43534</v>
-          </cell>
-          <cell r="F7">
-            <v>26517</v>
-          </cell>
-          <cell r="G7">
-            <v>38391</v>
-          </cell>
-          <cell r="H7">
-            <v>51942</v>
-          </cell>
-          <cell r="I7">
-            <v>32611</v>
-          </cell>
-          <cell r="J7">
-            <v>45304</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="7">
-        <row r="10">
-          <cell r="E10">
-            <v>27053</v>
-          </cell>
-          <cell r="F10">
-            <v>65053</v>
-          </cell>
-          <cell r="G10">
-            <v>65608</v>
-          </cell>
-          <cell r="H10">
-            <v>88014</v>
-          </cell>
-          <cell r="I10">
-            <v>59085</v>
-          </cell>
-          <cell r="J10">
-            <v>60005</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="8">
-        <row r="6">
-          <cell r="C6">
-            <v>22965</v>
-          </cell>
-          <cell r="D6">
-            <v>21773</v>
-          </cell>
-          <cell r="E6">
-            <v>15444</v>
-          </cell>
-          <cell r="F6">
-            <v>20007</v>
-          </cell>
-          <cell r="G6">
-            <v>27463</v>
-          </cell>
-          <cell r="H6">
-            <v>8218</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="C7">
-            <v>2359</v>
-          </cell>
-          <cell r="D7">
-            <v>4144</v>
-          </cell>
-          <cell r="E7">
-            <v>3229</v>
-          </cell>
-          <cell r="F7">
-            <v>3192</v>
-          </cell>
-          <cell r="G7">
-            <v>2122</v>
-          </cell>
-          <cell r="H7">
-            <v>2340</v>
-          </cell>
-          <cell r="I7">
-            <v>2999</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="C8">
-            <v>38384</v>
-          </cell>
-          <cell r="D8">
-            <v>18655</v>
-          </cell>
-          <cell r="E8">
-            <v>32331</v>
-          </cell>
-          <cell r="F8">
-            <v>29111</v>
-          </cell>
-          <cell r="G8">
-            <v>26525</v>
-          </cell>
-          <cell r="H8">
-            <v>21670</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="C9">
-            <v>2817</v>
-          </cell>
-          <cell r="D9">
-            <v>3044</v>
-          </cell>
-          <cell r="E9">
-            <v>3923</v>
-          </cell>
-          <cell r="F9">
-            <v>4464</v>
-          </cell>
-          <cell r="G9">
-            <v>1814</v>
-          </cell>
-          <cell r="H9">
-            <v>2832</v>
-          </cell>
-          <cell r="I9">
-            <v>3098</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="C10">
-            <v>16075</v>
-          </cell>
-          <cell r="D10">
-            <v>15805</v>
-          </cell>
-          <cell r="E10">
-            <v>17535</v>
-          </cell>
-          <cell r="F10">
-            <v>8229</v>
-          </cell>
-          <cell r="G10">
-            <v>19313</v>
-          </cell>
-          <cell r="H10">
-            <v>5096</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="C11">
-            <v>10230</v>
-          </cell>
-          <cell r="D11">
-            <v>14418</v>
-          </cell>
-          <cell r="E11">
-            <v>12421</v>
-          </cell>
-          <cell r="F11">
-            <v>10881</v>
-          </cell>
-          <cell r="G11">
-            <v>16950</v>
-          </cell>
-          <cell r="H11">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="9">
-        <row r="15">
-          <cell r="K15">
-            <v>16570</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="10">
-        <row r="11">
-          <cell r="E11">
-            <v>19349</v>
-          </cell>
-          <cell r="F11">
-            <v>34006</v>
-          </cell>
-          <cell r="G11">
-            <v>31406</v>
-          </cell>
-          <cell r="H11">
-            <v>49884</v>
-          </cell>
-          <cell r="I11">
-            <v>31803</v>
-          </cell>
-          <cell r="J11">
-            <v>39846</v>
-          </cell>
-          <cell r="K11">
-            <v>37424</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="11">
-        <row r="13">
-          <cell r="E13">
-            <v>18271</v>
-          </cell>
-          <cell r="F13">
-            <v>18567</v>
-          </cell>
-          <cell r="G13">
-            <v>30849</v>
-          </cell>
-          <cell r="H13">
-            <v>30055</v>
-          </cell>
-          <cell r="I13">
-            <v>52803</v>
-          </cell>
-          <cell r="J13">
-            <v>45389</v>
-          </cell>
-          <cell r="K13">
-            <v>35313</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Sapori Produccion Mensual"/>
@@ -598,233 +199,107 @@
       <sheetName val="Gelatina"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
       <sheetData sheetId="2">
         <row r="12">
-          <cell r="O12">
-            <v>578361</v>
-          </cell>
-          <cell r="P12">
-            <v>687903</v>
-          </cell>
           <cell r="Q12">
-            <v>31326</v>
+            <v>132472</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="3">
         <row r="9">
-          <cell r="V9">
-            <v>500217</v>
-          </cell>
-          <cell r="W9">
-            <v>577194</v>
-          </cell>
           <cell r="X9">
-            <v>29574</v>
+            <v>113655</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="4">
         <row r="9">
-          <cell r="L9">
-            <v>498292</v>
-          </cell>
           <cell r="M9">
-            <v>23624</v>
+            <v>98902</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="5"/>
+      <sheetData sheetId="5" refreshError="1"/>
       <sheetData sheetId="6">
         <row r="7">
-          <cell r="K7">
-            <v>44970</v>
-          </cell>
-          <cell r="L7">
-            <v>54128</v>
-          </cell>
           <cell r="M7">
-            <v>2095</v>
+            <v>7792</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="7">
         <row r="10">
-          <cell r="K10">
-            <v>70627</v>
+          <cell r="L10">
+            <v>14762</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="8">
         <row r="6">
-          <cell r="I6">
-            <v>15181</v>
-          </cell>
-          <cell r="J6">
-            <v>19404</v>
+          <cell r="K6">
+            <v>6221</v>
           </cell>
         </row>
         <row r="7">
-          <cell r="J7">
-            <v>3221</v>
+          <cell r="K7">
+            <v>799</v>
           </cell>
         </row>
         <row r="8">
-          <cell r="I8">
-            <v>24605</v>
-          </cell>
-          <cell r="J8">
-            <v>31637</v>
+          <cell r="K8">
+            <v>7134</v>
           </cell>
         </row>
         <row r="9">
-          <cell r="J9">
-            <v>3881</v>
+          <cell r="K9">
+            <v>1034</v>
           </cell>
         </row>
         <row r="10">
-          <cell r="I10">
-            <v>12002</v>
-          </cell>
-          <cell r="J10">
-            <v>11277</v>
+          <cell r="K10">
+            <v>5495</v>
           </cell>
         </row>
         <row r="11">
-          <cell r="I11">
-            <v>12086</v>
-          </cell>
-          <cell r="J11">
-            <v>8830</v>
+          <cell r="K11">
+            <v>5365</v>
           </cell>
         </row>
         <row r="12">
-          <cell r="I12">
-            <v>7967</v>
-          </cell>
-          <cell r="J12">
-            <v>4094</v>
+          <cell r="K12">
+            <v>1973</v>
           </cell>
         </row>
         <row r="13">
-          <cell r="I13">
-            <v>7892</v>
-          </cell>
-          <cell r="J13">
-            <v>4163</v>
+          <cell r="K13">
+            <v>1981</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="9">
         <row r="18">
-          <cell r="E18">
-            <v>222793</v>
-          </cell>
-          <cell r="F18">
-            <v>98244</v>
-          </cell>
-          <cell r="G18">
-            <v>173801</v>
-          </cell>
-          <cell r="H18">
-            <v>192306</v>
-          </cell>
-          <cell r="I18">
-            <v>164217</v>
-          </cell>
-          <cell r="J18">
-            <v>194544</v>
-          </cell>
-          <cell r="K18">
-            <v>239872</v>
-          </cell>
-          <cell r="L18">
-            <v>253860</v>
+          <cell r="M18">
+            <v>27530</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="10">
         <row r="11">
-          <cell r="L11">
-            <v>52480</v>
+          <cell r="M11">
+            <v>6248</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="11">
         <row r="13">
-          <cell r="L13">
-            <v>53734</v>
+          <cell r="M13">
+            <v>8761</v>
           </cell>
         </row>
       </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Balance Sapori vs Inventario"/>
-      <sheetName val="INFOGRAFIA"/>
-      <sheetName val="Balance Vs Ventas"/>
-      <sheetName val="Comparativo Sales LT vs MTD Pro"/>
-      <sheetName val="Programacion"/>
-      <sheetName val="Escenarios de Alcance"/>
-      <sheetName val="RESUMEN MAYO 26"/>
-      <sheetName val="Resumen Inventarios ABRIL 26"/>
-      <sheetName val="PRODUCCION DIARIA AGOSTO 2026"/>
-      <sheetName val="RESUMEN Y GRÁFICOS"/>
-      <sheetName val="Produccion MTD SHARE"/>
-      <sheetName val="DASHBOARD"/>
-      <sheetName val="Foto Cierre Semana 06-1004"/>
-      <sheetName val="Foto Cierre Semana 13-1726"/>
-      <sheetName val="Foto Cierre Semana 16-2026"/>
-      <sheetName val="Formula"/>
-      <sheetName val="RESUMEN COP BY SKU"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="4">
-          <cell r="D4">
-            <v>37424</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2">
-        <row r="24">
-          <cell r="C24">
-            <v>76012</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8">
-        <row r="88">
-          <cell r="AD88">
-            <v>437902</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1171,74 +646,59 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <f>'[1]Total Unidades Mensuales'!I12</f>
         <v>520938</v>
       </c>
       <c r="B3">
-        <f>'[1]Total Unidades Mensuales'!J12</f>
         <v>413087</v>
       </c>
       <c r="C3">
-        <f>'[1]Total Unidades Mensuales'!K12</f>
         <v>535420</v>
       </c>
       <c r="D3">
-        <f>'[1]Total Unidades Mensuales'!L12</f>
         <v>564513</v>
       </c>
       <c r="E3">
-        <f>'[1]Total Unidades Mensuales'!M12</f>
         <v>609205</v>
       </c>
       <c r="F3" s="2">
-        <f>'[1]Total Unidades Mensuales'!$N$12</f>
         <v>518837</v>
       </c>
       <c r="G3" s="9">
-        <f>'[2]Total Unidades Mensuales'!$O$12</f>
         <v>578361</v>
       </c>
       <c r="H3" s="2">
-        <f>'[2]Total Unidades Mensuales'!$P$12</f>
         <v>687903</v>
       </c>
       <c r="I3" s="2">
-        <f>'[2]Total Unidades Mensuales'!$Q$12</f>
-        <v>31326</v>
+        <f>'[1]Total Unidades Mensuales'!$Q$12</f>
+        <v>132472</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B4" s="3">
-        <f>'[1]Total Unidades Mensuales'!J13</f>
         <v>-0.2070323147860206</v>
       </c>
       <c r="C4" s="3">
-        <f>'[1]Total Unidades Mensuales'!K13</f>
         <v>0.29614342741359567</v>
       </c>
       <c r="D4" s="3">
-        <f>'[1]Total Unidades Mensuales'!L13</f>
         <v>5.4336782339098277E-2</v>
       </c>
       <c r="E4" s="3">
-        <f>'[1]Total Unidades Mensuales'!M13</f>
         <v>7.9169124537433147E-2</v>
       </c>
       <c r="F4" s="3">
-        <f>'[1]Total Unidades Mensuales'!N13</f>
         <v>-0.14833758751159298</v>
       </c>
       <c r="G4" s="3">
-        <f>(G3-F3)/F3</f>
         <v>0.11472581947702265</v>
       </c>
       <c r="H4" s="3">
-        <f>(H3-G3)/G3</f>
         <v>0.18940073760160175</v>
       </c>
       <c r="I4" s="3">
         <f>(I3-H3)/H3</f>
-        <v>-0.95446160287133508</v>
+        <v>-0.80742633772494088</v>
       </c>
     </row>
   </sheetData>
@@ -1251,10 +711,10 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67F921FD-1DF5-467A-8795-A0197415D027}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>9</v>
       </c>
@@ -1264,7 +724,7 @@
       <c r="E1" s="12"/>
       <c r="F1" s="12"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46054</v>
       </c>
@@ -1289,70 +749,66 @@
       <c r="H2" s="5">
         <v>46266</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="5">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <f>[1]Gelatina!E13</f>
         <v>18271</v>
       </c>
       <c r="B3" s="2">
-        <f>[1]Gelatina!F13</f>
         <v>18567</v>
       </c>
       <c r="C3" s="2">
-        <f>[1]Gelatina!G13</f>
         <v>30849</v>
       </c>
       <c r="D3" s="2">
-        <f>[1]Gelatina!H13</f>
         <v>30055</v>
       </c>
       <c r="E3" s="2">
-        <f>[1]Gelatina!I13</f>
         <v>52803</v>
       </c>
       <c r="F3" s="2">
-        <f>[1]Gelatina!J13</f>
         <v>45389</v>
       </c>
       <c r="G3" s="2">
-        <f>[1]Gelatina!$K$13</f>
         <v>35313</v>
       </c>
       <c r="H3" s="2">
-        <f>[2]Gelatina!$L$13</f>
         <v>53734</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I3" s="2">
+        <f>[1]Gelatina!$M$13</f>
+        <v>8761</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="4">
-        <f>(B3-A3)/A3</f>
         <v>1.6200536369109519E-2</v>
       </c>
       <c r="C4" s="4">
-        <f>(C3-B3)/B3</f>
         <v>0.66149620294070122</v>
       </c>
       <c r="D4" s="4">
-        <f t="shared" ref="D4:H4" si="0">(D3-C3)/C3</f>
         <v>-2.5738273525884144E-2</v>
       </c>
       <c r="E4" s="4">
-        <f t="shared" si="0"/>
         <v>0.75687905506571285</v>
       </c>
       <c r="F4" s="4">
-        <f t="shared" si="0"/>
         <v>-0.14040868890025188</v>
       </c>
       <c r="G4" s="4">
-        <f t="shared" si="0"/>
         <v>-0.22199211262640728</v>
       </c>
       <c r="H4" s="4">
-        <f t="shared" si="0"/>
         <v>0.5216492509840569</v>
+      </c>
+      <c r="I4" s="4">
+        <f t="shared" ref="I4" si="0">(I3-H3)/H3</f>
+        <v>-0.83695611716976215</v>
       </c>
     </row>
   </sheetData>
@@ -1409,78 +865,62 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
-        <f>'[1]Total Cremigurt Unidades'!P9</f>
         <v>466290</v>
       </c>
       <c r="B3">
-        <f>'[1]Total Cremigurt Unidades'!Q9</f>
         <v>321987</v>
       </c>
       <c r="C3">
-        <f>'[1]Total Cremigurt Unidades'!R9</f>
         <v>445909</v>
       </c>
       <c r="D3">
-        <f>'[1]Total Cremigurt Unidades'!S9</f>
         <v>449661</v>
       </c>
       <c r="E3">
-        <f>'[1]Total Cremigurt Unidades'!T9</f>
         <v>518112</v>
       </c>
       <c r="F3">
-        <f>'[1]Total Cremigurt Unidades'!U9</f>
         <v>429574</v>
       </c>
       <c r="G3" s="6">
-        <f>'[2]Total Cremigurt Unidades'!$V$9</f>
         <v>500217</v>
       </c>
       <c r="H3" s="2">
-        <f>'[2]Total Cremigurt Unidades'!$W$9</f>
         <v>577194</v>
       </c>
-      <c r="I3">
-        <f>'[2]Total Cremigurt Unidades'!$X$9</f>
-        <v>29574</v>
+      <c r="I3" s="2">
+        <f>'[1]Total Cremigurt Unidades'!$X$9</f>
+        <v>113655</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <f>'[1]Total Cremigurt Unidades'!P10</f>
         <v>0.47828650777044379</v>
       </c>
       <c r="B4" s="3">
-        <f>'[1]Total Cremigurt Unidades'!Q10</f>
         <v>-0.30947050119024644</v>
       </c>
       <c r="C4" s="3">
-        <f>'[1]Total Cremigurt Unidades'!R10</f>
         <v>0.38486646976430727</v>
       </c>
       <c r="D4" s="3">
-        <f>'[1]Total Cremigurt Unidades'!S10</f>
         <v>8.4142728673339186E-3</v>
       </c>
       <c r="E4" s="3">
-        <f>'[1]Total Cremigurt Unidades'!T10</f>
         <v>0.15222801176886588</v>
       </c>
       <c r="F4" s="3">
-        <f>'[1]Total Cremigurt Unidades'!U10</f>
         <v>-0.17088583163485888</v>
       </c>
       <c r="G4" s="7">
-        <f>(G3-F3)/F3</f>
         <v>0.16444896571952677</v>
       </c>
       <c r="H4" s="7">
-        <f>(H3-G3)/G3</f>
         <v>0.15388721294957988</v>
       </c>
       <c r="I4" s="7">
         <f>(I3-H3)/H3</f>
-        <v>-0.94876246114824481</v>
+        <v>-0.80309046871589107</v>
       </c>
     </row>
   </sheetData>
@@ -1537,75 +977,60 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
-        <f>'[1]150 gr'!E9</f>
         <v>386904</v>
       </c>
       <c r="B3">
-        <f>'[1]150 gr'!F9</f>
         <v>265359</v>
       </c>
       <c r="C3">
-        <f>'[1]150 gr'!G9</f>
         <v>386551</v>
       </c>
       <c r="D3">
-        <f>'[1]150 gr'!H9</f>
         <v>383814</v>
       </c>
       <c r="E3">
-        <f>'[1]150 gr'!I9</f>
         <v>461320</v>
       </c>
       <c r="F3">
-        <f>'[1]150 gr'!J9</f>
         <v>357059</v>
       </c>
       <c r="G3" s="10">
-        <f>'[3]PRODUCCION DIARIA AGOSTO 2026'!$AD$88</f>
         <v>437902</v>
       </c>
       <c r="H3" s="2">
-        <f>'[2]150 gr'!$L$9</f>
         <v>498292</v>
       </c>
       <c r="I3" s="2">
-        <f>'[2]150 gr'!$M$9</f>
-        <v>23624</v>
+        <f>'[1]150 gr'!$M$9</f>
+        <v>98902</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3">
-        <f>'[1]150 gr'!F7</f>
         <v>-0.31414769555238509</v>
       </c>
       <c r="C4" s="3">
-        <f>'[1]150 gr'!G7</f>
         <v>0.45670958965024738</v>
       </c>
       <c r="D4" s="3">
-        <f>'[1]150 gr'!H7</f>
         <v>-7.0805663418281161E-3</v>
       </c>
       <c r="E4" s="3">
-        <f>'[1]150 gr'!I7</f>
         <v>0.20193635458842044</v>
       </c>
       <c r="F4" s="3">
-        <f>'[1]150 gr'!J7</f>
         <v>-0.22600580941645712</v>
       </c>
       <c r="G4" s="3">
-        <f>'[1]150 gr'!K7</f>
         <v>0.22641356190433515</v>
       </c>
       <c r="H4" s="7">
-        <f>(H3-G3)/G3</f>
         <v>0.13790756836004403</v>
       </c>
       <c r="I4" s="7">
         <f>(I3-H3)/H3</f>
-        <v>-0.95259004760261057</v>
+        <v>-0.80151798543825714</v>
       </c>
     </row>
   </sheetData>
@@ -1662,75 +1087,60 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
-        <f>'[1]700 gr'!E7</f>
         <v>43534</v>
       </c>
       <c r="B3">
-        <f>'[1]700 gr'!F7</f>
         <v>26517</v>
       </c>
       <c r="C3">
-        <f>'[1]700 gr'!G7</f>
         <v>38391</v>
       </c>
       <c r="D3">
-        <f>'[1]700 gr'!H7</f>
         <v>51942</v>
       </c>
       <c r="E3">
-        <f>'[1]700 gr'!I7</f>
         <v>32611</v>
       </c>
       <c r="F3">
-        <f>'[1]700 gr'!J7</f>
         <v>45304</v>
       </c>
       <c r="G3" s="10">
-        <f>'[2]700 gr'!$K$7</f>
         <v>44970</v>
       </c>
       <c r="H3" s="2">
-        <f>'[2]700 gr'!$L$7</f>
         <v>54128</v>
       </c>
       <c r="I3" s="2">
-        <f>'[2]700 gr'!$M$7</f>
-        <v>2095</v>
+        <f>'[1]700 gr'!$M$7</f>
+        <v>7792</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3">
-        <f>'[1]700 gr'!F5</f>
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <f>'[1]700 gr'!G5</f>
         <v>0</v>
       </c>
       <c r="D4" s="3">
-        <f>'[1]700 gr'!H5</f>
         <v>0</v>
       </c>
       <c r="E4" s="3">
-        <f>'[1]700 gr'!I5</f>
         <v>-0.37216510723499285</v>
       </c>
       <c r="F4" s="3">
-        <f>'[1]700 gr'!J5</f>
         <v>0.38922449480236732</v>
       </c>
       <c r="G4" s="3">
-        <f>'[1]700 gr'!K5</f>
         <v>-7.372417446583083E-3</v>
       </c>
       <c r="H4" s="7">
-        <f>(H3-G3)/G3</f>
         <v>0.20364687569490772</v>
       </c>
       <c r="I4" s="7">
         <f>(I3-H3)/H3</f>
-        <v>-0.9612954478273722</v>
+        <v>-0.85604493053502806</v>
       </c>
     </row>
   </sheetData>
@@ -1743,10 +1153,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50800131-7A3A-4EA9-BC89-BE76C1CC5304}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>4</v>
       </c>
@@ -1756,7 +1166,7 @@
       <c r="E1" s="12"/>
       <c r="F1" s="12"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46054</v>
       </c>
@@ -1781,66 +1191,64 @@
       <c r="H2" s="5">
         <v>46266</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="5">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>0</v>
       </c>
       <c r="B3" s="2">
-        <f>'[1]Linea Azul'!E10</f>
         <v>27053</v>
       </c>
       <c r="C3" s="2">
-        <f>'[1]Linea Azul'!F10</f>
         <v>65053</v>
       </c>
       <c r="D3" s="2">
-        <f>'[1]Linea Azul'!G10</f>
         <v>65608</v>
       </c>
       <c r="E3" s="2">
-        <f>'[1]Linea Azul'!H10</f>
         <v>88014</v>
       </c>
       <c r="F3" s="2">
-        <f>'[1]Linea Azul'!I10</f>
         <v>59085</v>
       </c>
       <c r="G3" s="2">
-        <f>'[1]Linea Azul'!$J$10</f>
         <v>60005</v>
       </c>
       <c r="H3" s="2">
-        <f>'[2]Linea Azul'!$K$10</f>
         <v>70627</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I3" s="2">
+        <f>'[1]Linea Azul'!$L$10</f>
+        <v>14762</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="4">
-        <f>(C3-B3)/B3</f>
         <v>1.4046501312238939</v>
       </c>
       <c r="D4" s="4">
-        <f t="shared" ref="D4:H4" si="0">(D3-C3)/C3</f>
         <v>8.5315050804728454E-3</v>
       </c>
       <c r="E4" s="4">
-        <f t="shared" si="0"/>
         <v>0.34151323009389101</v>
       </c>
       <c r="F4" s="4">
-        <f t="shared" si="0"/>
         <v>-0.3286863453541482</v>
       </c>
       <c r="G4" s="4">
-        <f t="shared" si="0"/>
         <v>1.557078784801557E-2</v>
       </c>
       <c r="H4" s="4">
-        <f t="shared" si="0"/>
         <v>0.17701858178485128</v>
+      </c>
+      <c r="I4" s="4">
+        <f t="shared" ref="I4" si="0">(I3-H3)/H3</f>
+        <v>-0.79098644994124057</v>
       </c>
     </row>
   </sheetData>
@@ -1853,10 +1261,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA85D05B-3ECD-40A5-BED5-A9D687E905B1}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>6</v>
       </c>
@@ -1866,7 +1274,7 @@
       <c r="E1" s="12"/>
       <c r="F1" s="12"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46054</v>
       </c>
@@ -1891,70 +1299,66 @@
       <c r="H2" s="11">
         <v>46266</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="11">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <f>[1]POWER!$C$6+[1]POWER!$C$8+[1]POWER!$C$10+[1]POWER!$C$11</f>
         <v>87654</v>
       </c>
       <c r="B3" s="2">
-        <f>[1]POWER!$D$6+[1]POWER!$D$8+[1]POWER!$D$10+[1]POWER!$D$11</f>
         <v>70651</v>
       </c>
       <c r="C3" s="2">
-        <f>[1]POWER!$E$6+[1]POWER!$E$8+[1]POWER!$E$10+[1]POWER!$E$11</f>
         <v>77731</v>
       </c>
       <c r="D3" s="2">
-        <f>[1]POWER!$F$6+[1]POWER!$F$8+[1]POWER!$F$10+[1]POWER!$F$11</f>
         <v>68228</v>
       </c>
       <c r="E3" s="2">
-        <f>[1]POWER!$G$6+[1]POWER!$G$8+[1]POWER!$G$10+[1]POWER!$G$11</f>
         <v>90251</v>
       </c>
       <c r="F3" s="2">
-        <f>[1]POWER!$H$6+[1]POWER!$H$8+[1]POWER!$H$10+[1]POWER!$H$11</f>
         <v>34984</v>
       </c>
       <c r="G3" s="2">
-        <f>[2]POWER!$I$6+[2]POWER!$I$8+[2]POWER!$I$10+[2]POWER!$I$11+[2]POWER!$I$12+[2]POWER!$I$13</f>
         <v>79733</v>
       </c>
       <c r="H3" s="2">
-        <f>[2]POWER!$J$6+[2]POWER!$J$8+[2]POWER!$J$10+[2]POWER!$J$11+[2]POWER!$J$12+[2]POWER!$J$13</f>
         <v>79405</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I3" s="2">
+        <f>+[1]POWER!$K$6+[1]POWER!$K$8+[1]POWER!$K$10+[1]POWER!$K$11+[1]POWER!$K$12+[1]POWER!$K$13</f>
+        <v>28169</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="4">
-        <f>(B3-A3)/A3</f>
         <v>-0.19397859766810413</v>
       </c>
       <c r="C4" s="4">
-        <f>(C3-B3)/B3</f>
         <v>0.10021089581180734</v>
       </c>
       <c r="D4" s="4">
-        <f t="shared" ref="D4:H4" si="0">(D3-C3)/C3</f>
         <v>-0.12225495619508304</v>
       </c>
       <c r="E4" s="4">
-        <f t="shared" si="0"/>
         <v>0.32278536671161401</v>
       </c>
       <c r="F4" s="4">
-        <f t="shared" si="0"/>
         <v>-0.61236994603937911</v>
       </c>
       <c r="G4" s="4">
-        <f t="shared" si="0"/>
         <v>1.2791276011891151</v>
       </c>
       <c r="H4" s="4">
-        <f t="shared" si="0"/>
         <v>-4.1137295724480456E-3</v>
+      </c>
+      <c r="I4" s="4">
+        <f t="shared" ref="I4" si="0">(I3-H3)/H3</f>
+        <v>-0.64524903973301428</v>
       </c>
     </row>
   </sheetData>
@@ -1967,10 +1371,10 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04414C49-388F-40D7-B11A-32B8FBF66B8E}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>5</v>
       </c>
@@ -1980,7 +1384,7 @@
       <c r="E1" s="12"/>
       <c r="F1" s="12"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46054</v>
       </c>
@@ -2005,70 +1409,66 @@
       <c r="H2" s="11">
         <v>46266</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="11">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <f>[1]POWER!$C$7+[1]POWER!$C$9</f>
         <v>5176</v>
       </c>
       <c r="B3" s="2">
-        <f>[1]POWER!$D$7+[1]POWER!$D$9</f>
         <v>7188</v>
       </c>
       <c r="C3" s="2">
-        <f>[1]POWER!$E$7+[1]POWER!$E$9</f>
         <v>7152</v>
       </c>
       <c r="D3" s="2">
-        <f>[1]POWER!$F$7+[1]POWER!$F$9</f>
         <v>7656</v>
       </c>
       <c r="E3" s="2">
-        <f>[1]POWER!$G$7+[1]POWER!$G$9</f>
         <v>3936</v>
       </c>
       <c r="F3" s="2">
-        <f>[1]POWER!$H$7+[1]POWER!$H$9</f>
         <v>5172</v>
       </c>
       <c r="G3" s="2">
-        <f>+[1]POWER!$I$7+[1]POWER!$I$9</f>
         <v>6097</v>
       </c>
       <c r="H3" s="2">
-        <f>[2]POWER!$J$7+[2]POWER!$J$9</f>
         <v>7102</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I3" s="2">
+        <f>+[1]POWER!$K$7+[1]POWER!$K$9</f>
+        <v>1833</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="4">
-        <f>(B3-A3)/A3</f>
         <v>0.38871715610510044</v>
       </c>
       <c r="C4" s="4">
-        <f>(C3-B3)/B3</f>
         <v>-5.008347245409015E-3</v>
       </c>
       <c r="D4" s="4">
-        <f t="shared" ref="D4:H4" si="0">(D3-C3)/C3</f>
         <v>7.0469798657718116E-2</v>
       </c>
       <c r="E4" s="4">
-        <f t="shared" si="0"/>
         <v>-0.48589341692789967</v>
       </c>
       <c r="F4" s="4">
-        <f t="shared" si="0"/>
         <v>0.31402439024390244</v>
       </c>
       <c r="G4" s="4">
-        <f t="shared" si="0"/>
         <v>0.1788476411446249</v>
       </c>
       <c r="H4" s="4">
-        <f t="shared" si="0"/>
         <v>0.16483516483516483</v>
+      </c>
+      <c r="I4" s="4">
+        <f t="shared" ref="I4" si="0">(I3-H3)/H3</f>
+        <v>-0.74190368910166149</v>
       </c>
     </row>
   </sheetData>
@@ -2081,10 +1481,10 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1607DE2-0B78-461F-9558-D9AD76E0CDAB}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>7</v>
       </c>
@@ -2094,7 +1494,7 @@
       <c r="E1" s="12"/>
       <c r="F1" s="12"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46054</v>
       </c>
@@ -2119,70 +1519,66 @@
       <c r="H2" s="11">
         <v>46266</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="11">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <f>[2]Frutas!$E$18</f>
         <v>222793</v>
       </c>
       <c r="B3" s="2">
-        <f>[2]Frutas!$F$18</f>
         <v>98244</v>
       </c>
       <c r="C3" s="2">
-        <f>[2]Frutas!$G$18</f>
         <v>173801</v>
       </c>
       <c r="D3" s="2">
-        <f>[2]Frutas!$H$18</f>
         <v>192306</v>
       </c>
       <c r="E3" s="2">
-        <f>[2]Frutas!$I$18</f>
         <v>164217</v>
       </c>
       <c r="F3" s="2">
-        <f>[2]Frutas!$J$18</f>
         <v>194544</v>
       </c>
       <c r="G3" s="2">
-        <f>[2]Frutas!$K$18</f>
         <v>239872</v>
       </c>
       <c r="H3" s="2">
-        <f>[2]Frutas!$L$18</f>
         <v>253860</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I3" s="2">
+        <f>[1]Frutas!$M$18</f>
+        <v>27530</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="4">
-        <f>(B3-A3)/A3</f>
         <v>-0.55903461957960976</v>
       </c>
       <c r="C4" s="4">
-        <f>(C3-B3)/B3</f>
         <v>0.76907495623142386</v>
       </c>
       <c r="D4" s="4">
-        <f t="shared" ref="D4:H4" si="0">(D3-C3)/C3</f>
         <v>0.10647234480814265</v>
       </c>
       <c r="E4" s="4">
-        <f t="shared" si="0"/>
         <v>-0.14606408536395121</v>
       </c>
       <c r="F4" s="4">
-        <f t="shared" si="0"/>
         <v>0.18467637333528197</v>
       </c>
       <c r="G4" s="4">
-        <f t="shared" si="0"/>
         <v>0.23299613455053869</v>
       </c>
       <c r="H4" s="4">
-        <f t="shared" si="0"/>
         <v>5.8314434364994665E-2</v>
+      </c>
+      <c r="I4" s="4">
+        <f t="shared" ref="I4" si="0">(I3-H3)/H3</f>
+        <v>-0.89155440006302689</v>
       </c>
     </row>
   </sheetData>
@@ -2195,10 +1591,10 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76579A32-DE1B-43F8-A9E1-7A0C474A6180}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>8</v>
       </c>
@@ -2208,7 +1604,7 @@
       <c r="E1" s="12"/>
       <c r="F1" s="12"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>46054</v>
       </c>
@@ -2233,70 +1629,66 @@
       <c r="H2" s="5">
         <v>46266</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="5">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <f>[1]Cremosillo!E11</f>
         <v>19349</v>
       </c>
       <c r="B3" s="2">
-        <f>[1]Cremosillo!F11</f>
         <v>34006</v>
       </c>
       <c r="C3" s="2">
-        <f>[1]Cremosillo!G11</f>
         <v>31406</v>
       </c>
       <c r="D3" s="2">
-        <f>[1]Cremosillo!H11</f>
         <v>49884</v>
       </c>
       <c r="E3" s="2">
-        <f>[1]Cremosillo!I11</f>
         <v>31803</v>
       </c>
       <c r="F3" s="2">
-        <f>[1]Cremosillo!J11</f>
         <v>39846</v>
       </c>
       <c r="G3" s="2">
-        <f>[1]Cremosillo!$K$11</f>
         <v>37424</v>
       </c>
       <c r="H3" s="2">
-        <f>[2]Cremosillo!$L$11</f>
         <v>52480</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I3" s="2">
+        <f>[1]Cremosillo!$M$11</f>
+        <v>6248</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="4">
-        <f>(B3-A3)/A3</f>
         <v>0.75750684789911626</v>
       </c>
       <c r="C4" s="4">
-        <f>(C3-B3)/B3</f>
         <v>-7.6457095806622355E-2</v>
       </c>
       <c r="D4" s="4">
-        <f t="shared" ref="D4:H4" si="0">(D3-C3)/C3</f>
         <v>0.58835891230974968</v>
       </c>
       <c r="E4" s="4">
-        <f t="shared" si="0"/>
         <v>-0.36246090930959829</v>
       </c>
       <c r="F4" s="4">
-        <f t="shared" si="0"/>
         <v>0.25290066974813696</v>
       </c>
       <c r="G4" s="4">
-        <f t="shared" si="0"/>
         <v>-6.0784018471113789E-2</v>
       </c>
       <c r="H4" s="4">
-        <f t="shared" si="0"/>
         <v>0.40230867892261651</v>
+      </c>
+      <c r="I4" s="4">
+        <f t="shared" ref="I4" si="0">(I3-H3)/H3</f>
+        <v>-0.88094512195121955</v>
       </c>
     </row>
   </sheetData>

--- a/data/Historico_Produccion_CREMIGURT.xlsx
+++ b/data/Historico_Produccion_CREMIGURT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\SUPPLY CHAIN\dashboard_supply_v.2.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5237397-39DC-4610-B4B4-E3FE9FAD8587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{ACB42D87-93D0-4626-9D9E-6EFF9151893F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5FCEDCA6-54A6-483C-946E-D02D6DFB3A06}"/>
   </bookViews>
@@ -28,6 +28,7 @@
     <externalReference r:id="rId11"/>
   </externalReferences>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -204,21 +205,21 @@
       <sheetData sheetId="2">
         <row r="12">
           <cell r="Q12">
-            <v>132472</v>
+            <v>625159</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="3">
         <row r="9">
           <cell r="X9">
-            <v>113655</v>
+            <v>548454</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="4">
         <row r="9">
           <cell r="M9">
-            <v>98902</v>
+            <v>479880</v>
           </cell>
         </row>
       </sheetData>
@@ -226,77 +227,77 @@
       <sheetData sheetId="6">
         <row r="7">
           <cell r="M7">
-            <v>7792</v>
+            <v>44662</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="7">
         <row r="10">
           <cell r="L10">
-            <v>14762</v>
+            <v>58041</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="8">
         <row r="6">
           <cell r="K6">
-            <v>6221</v>
+            <v>15074</v>
           </cell>
         </row>
         <row r="7">
           <cell r="K7">
-            <v>799</v>
+            <v>2509</v>
           </cell>
         </row>
         <row r="8">
           <cell r="K8">
-            <v>7134</v>
+            <v>18168</v>
           </cell>
         </row>
         <row r="9">
           <cell r="K9">
-            <v>1034</v>
+            <v>3131</v>
           </cell>
         </row>
         <row r="10">
           <cell r="K10">
-            <v>5495</v>
+            <v>13537</v>
           </cell>
         </row>
         <row r="11">
           <cell r="K11">
-            <v>5365</v>
+            <v>15575</v>
           </cell>
         </row>
         <row r="12">
           <cell r="K12">
-            <v>1973</v>
+            <v>9537</v>
           </cell>
         </row>
         <row r="13">
           <cell r="K13">
-            <v>1981</v>
+            <v>5110</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="9">
         <row r="18">
           <cell r="M18">
-            <v>27530</v>
+            <v>263210</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="10">
         <row r="11">
           <cell r="M11">
-            <v>6248</v>
+            <v>30204</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="11">
         <row r="13">
           <cell r="M13">
-            <v>8761</v>
+            <v>37910</v>
           </cell>
         </row>
       </sheetData>
@@ -671,7 +672,7 @@
       </c>
       <c r="I3" s="2">
         <f>'[1]Total Unidades Mensuales'!$Q$12</f>
-        <v>132472</v>
+        <v>625159</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -698,7 +699,7 @@
       </c>
       <c r="I4" s="3">
         <f>(I3-H3)/H3</f>
-        <v>-0.80742633772494088</v>
+        <v>-9.1210534043317151E-2</v>
       </c>
     </row>
   </sheetData>
@@ -780,7 +781,7 @@
       </c>
       <c r="I3" s="2">
         <f>[1]Gelatina!$M$13</f>
-        <v>8761</v>
+        <v>37910</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -807,8 +808,8 @@
         <v>0.5216492509840569</v>
       </c>
       <c r="I4" s="4">
-        <f t="shared" ref="I4" si="0">(I3-H3)/H3</f>
-        <v>-0.83695611716976215</v>
+        <f>(I3-H3)/H3</f>
+        <v>-0.29448766144340643</v>
       </c>
     </row>
   </sheetData>
@@ -890,7 +891,7 @@
       </c>
       <c r="I3" s="2">
         <f>'[1]Total Cremigurt Unidades'!$X$9</f>
-        <v>113655</v>
+        <v>548454</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -920,7 +921,7 @@
       </c>
       <c r="I4" s="7">
         <f>(I3-H3)/H3</f>
-        <v>-0.80309046871589107</v>
+        <v>-4.9792617386875127E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1002,7 +1003,7 @@
       </c>
       <c r="I3" s="2">
         <f>'[1]150 gr'!$M$9</f>
-        <v>98902</v>
+        <v>479880</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -1030,7 +1031,7 @@
       </c>
       <c r="I4" s="7">
         <f>(I3-H3)/H3</f>
-        <v>-0.80151798543825714</v>
+        <v>-3.6950221958209239E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1112,7 +1113,7 @@
       </c>
       <c r="I3" s="2">
         <f>'[1]700 gr'!$M$7</f>
-        <v>7792</v>
+        <v>44662</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -1140,7 +1141,7 @@
       </c>
       <c r="I4" s="7">
         <f>(I3-H3)/H3</f>
-        <v>-0.85604493053502806</v>
+        <v>-0.17488176174992609</v>
       </c>
     </row>
   </sheetData>
@@ -1222,7 +1223,7 @@
       </c>
       <c r="I3" s="2">
         <f>'[1]Linea Azul'!$L$10</f>
-        <v>14762</v>
+        <v>58041</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -1247,8 +1248,8 @@
         <v>0.17701858178485128</v>
       </c>
       <c r="I4" s="4">
-        <f t="shared" ref="I4" si="0">(I3-H3)/H3</f>
-        <v>-0.79098644994124057</v>
+        <f>(I3-H3)/H3</f>
+        <v>-0.17820380307814293</v>
       </c>
     </row>
   </sheetData>
@@ -1330,7 +1331,7 @@
       </c>
       <c r="I3" s="2">
         <f>+[1]POWER!$K$6+[1]POWER!$K$8+[1]POWER!$K$10+[1]POWER!$K$11+[1]POWER!$K$12+[1]POWER!$K$13</f>
-        <v>28169</v>
+        <v>77001</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -1357,8 +1358,8 @@
         <v>-4.1137295724480456E-3</v>
       </c>
       <c r="I4" s="4">
-        <f t="shared" ref="I4" si="0">(I3-H3)/H3</f>
-        <v>-0.64524903973301428</v>
+        <f>(I3-H3)/H3</f>
+        <v>-3.0275171588690888E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1440,7 +1441,7 @@
       </c>
       <c r="I3" s="2">
         <f>+[1]POWER!$K$7+[1]POWER!$K$9</f>
-        <v>1833</v>
+        <v>5640</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -1467,8 +1468,8 @@
         <v>0.16483516483516483</v>
       </c>
       <c r="I4" s="4">
-        <f t="shared" ref="I4" si="0">(I3-H3)/H3</f>
-        <v>-0.74190368910166149</v>
+        <f>(I3-H3)/H3</f>
+        <v>-0.20585750492818924</v>
       </c>
     </row>
   </sheetData>
@@ -1550,7 +1551,7 @@
       </c>
       <c r="I3" s="2">
         <f>[1]Frutas!$M$18</f>
-        <v>27530</v>
+        <v>263210</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -1577,8 +1578,8 @@
         <v>5.8314434364994665E-2</v>
       </c>
       <c r="I4" s="4">
-        <f t="shared" ref="I4" si="0">(I3-H3)/H3</f>
-        <v>-0.89155440006302689</v>
+        <f>(I3-H3)/H3</f>
+        <v>3.6831324352005042E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1660,7 +1661,7 @@
       </c>
       <c r="I3" s="2">
         <f>[1]Cremosillo!$M$11</f>
-        <v>6248</v>
+        <v>30204</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -1687,8 +1688,8 @@
         <v>0.40230867892261651</v>
       </c>
       <c r="I4" s="4">
-        <f t="shared" ref="I4" si="0">(I3-H3)/H3</f>
-        <v>-0.88094512195121955</v>
+        <f>(I3-H3)/H3</f>
+        <v>-0.42446646341463412</v>
       </c>
     </row>
   </sheetData>
